--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_level.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_level.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3635" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3635" uniqueCount="435">
   <si>
     <t>等级</t>
   </si>
@@ -796,6 +796,9 @@
   </si>
   <si>
     <t>221</t>
+  </si>
+  <si>
+    <t>1#5|2#5|3#5|4#7|5#7|6#6|7#6</t>
   </si>
   <si>
     <t>222</t>
@@ -1355,9 +1358,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
+      <sz val="10"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1511,7 +1514,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1520,7 +1523,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFEBF1F8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1587,6 +1590,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1705,12 +1714,21 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1835,7 +1853,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1847,34 +1865,34 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1898,64 +1916,64 @@
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1964,14 +1982,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2515,12 +2533,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="5" s="1" customFormat="1" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B5" s="2">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -2528,12 +2546,12 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="6" s="1" customFormat="1" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="2">
-        <v>80</v>
+      <c r="B6" s="4">
+        <v>340</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>30</v>
@@ -2563,12 +2581,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="7" s="1" customFormat="1" spans="1:11">
       <c r="A7" s="1" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="2">
-        <v>200</v>
+        <v>640</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>30</v>
@@ -2598,12 +2616,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="8" s="1" customFormat="1" spans="1:11">
       <c r="A8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="2">
-        <v>330</v>
+      <c r="B8" s="4">
+        <v>1000</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>30</v>
@@ -2633,12 +2651,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="9" s="1" customFormat="1" spans="1:11">
       <c r="A9" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B9" s="2">
-        <v>400</v>
+        <v>1420</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>30</v>
@@ -2668,12 +2686,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="10" s="1" customFormat="1" spans="1:11">
       <c r="A10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="2">
-        <v>530</v>
+      <c r="B10" s="4">
+        <v>1900</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>30</v>
@@ -2703,12 +2721,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="11" s="1" customFormat="1" spans="1:11">
       <c r="A11" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B11" s="2">
-        <v>670</v>
+        <v>2440</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>30</v>
@@ -2738,12 +2756,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="12" s="1" customFormat="1" spans="1:11">
       <c r="A12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="2">
-        <v>800</v>
+      <c r="B12" s="4">
+        <v>3040</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>30</v>
@@ -2773,12 +2791,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="13" s="1" customFormat="1" spans="1:11">
       <c r="A13" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B13" s="2">
-        <v>800</v>
+        <v>3700</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>30</v>
@@ -2808,12 +2826,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="14" s="1" customFormat="1" spans="1:11">
       <c r="A14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="2">
-        <v>800</v>
+      <c r="B14" s="4">
+        <v>4420</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>30</v>
@@ -2843,12 +2861,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="15" s="1" customFormat="1" spans="1:11">
       <c r="A15" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B15" s="2">
-        <v>800</v>
+        <v>5200</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>30</v>
@@ -2878,12 +2896,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="16" s="1" customFormat="1" spans="1:11">
       <c r="A16" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="2">
-        <v>800</v>
+      <c r="B16" s="4">
+        <v>6040</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>30</v>
@@ -2913,12 +2931,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="17" s="1" customFormat="1" spans="1:11">
       <c r="A17" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B17" s="2">
-        <v>800</v>
+        <v>6940</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>30</v>
@@ -2948,12 +2966,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="18" s="1" customFormat="1" spans="1:11">
       <c r="A18" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="2">
-        <v>800</v>
+      <c r="B18" s="4">
+        <v>7900</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>30</v>
@@ -2983,12 +3001,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="19" s="1" customFormat="1" spans="1:11">
       <c r="A19" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B19" s="2">
-        <v>800</v>
+        <v>8920</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>30</v>
@@ -3018,12 +3036,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="20" s="1" customFormat="1" spans="1:11">
       <c r="A20" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="2">
-        <v>800</v>
+      <c r="B20" s="4">
+        <v>10000</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>30</v>
@@ -3053,12 +3071,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="21" s="1" customFormat="1" spans="1:11">
       <c r="A21" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B21" s="2">
-        <v>800</v>
+        <v>11140</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>30</v>
@@ -3088,12 +3106,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="22" s="1" customFormat="1" spans="1:11">
       <c r="A22" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="2">
-        <v>800</v>
+      <c r="B22" s="4">
+        <v>12340</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>30</v>
@@ -3123,12 +3141,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="23" s="1" customFormat="1" spans="1:11">
       <c r="A23" s="1" t="s">
         <v>52</v>
       </c>
       <c r="B23" s="2">
-        <v>1330</v>
+        <v>13600</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>30</v>
@@ -3158,12 +3176,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="24" s="1" customFormat="1" spans="1:11">
       <c r="A24" s="1" t="s">
         <v>53</v>
       </c>
       <c r="B24" s="4">
-        <v>5200</v>
+        <v>14920</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>30</v>
@@ -3193,12 +3211,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="25" s="1" customFormat="1" spans="1:11">
       <c r="A25" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B25" s="4">
-        <v>5500</v>
+      <c r="B25" s="2">
+        <v>16300</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>30</v>
@@ -3228,12 +3246,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="26" s="1" customFormat="1" spans="1:11">
       <c r="A26" s="1" t="s">
         <v>55</v>
       </c>
       <c r="B26" s="4">
-        <v>5800</v>
+        <v>17740</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>30</v>
@@ -3263,12 +3281,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="27" s="1" customFormat="1" spans="1:11">
       <c r="A27" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="4">
-        <v>6000</v>
+      <c r="B27" s="2">
+        <v>19240</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>30</v>
@@ -3298,12 +3316,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="28" s="1" customFormat="1" spans="1:11">
       <c r="A28" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B28" s="4">
-        <v>6300</v>
+        <v>20800</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>30</v>
@@ -3333,12 +3351,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="29" s="1" customFormat="1" spans="1:11">
       <c r="A29" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="4">
-        <v>6500</v>
+      <c r="B29" s="2">
+        <v>22420</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>30</v>
@@ -3368,12 +3386,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="30" s="1" customFormat="1" spans="1:11">
       <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B30" s="4">
-        <v>6800</v>
+        <v>24100</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>30</v>
@@ -3403,12 +3421,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="31" s="1" customFormat="1" spans="1:11">
       <c r="A31" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="4">
-        <v>7000</v>
+      <c r="B31" s="2">
+        <v>25840</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>30</v>
@@ -3438,12 +3456,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="32" s="1" customFormat="1" spans="1:11">
       <c r="A32" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B32" s="4">
-        <v>7300</v>
+        <v>27640</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>30</v>
@@ -3473,12 +3491,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="33" s="1" customFormat="1" spans="1:11">
       <c r="A33" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B33" s="4">
-        <v>7600</v>
+      <c r="B33" s="2">
+        <v>29500</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>30</v>
@@ -3508,12 +3526,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="34" s="1" customFormat="1" spans="1:11">
       <c r="A34" s="1" t="s">
         <v>63</v>
       </c>
       <c r="B34" s="4">
-        <v>13500</v>
+        <v>31420</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>30</v>
@@ -3543,12 +3561,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="35" s="1" customFormat="1" spans="1:11">
       <c r="A35" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B35" s="4">
-        <v>14200</v>
+      <c r="B35" s="2">
+        <v>33400</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>30</v>
@@ -3578,12 +3596,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="36" s="1" customFormat="1" spans="1:11">
       <c r="A36" s="1" t="s">
         <v>65</v>
       </c>
       <c r="B36" s="4">
-        <v>14800</v>
+        <v>35440</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>30</v>
@@ -3613,12 +3631,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="37" s="1" customFormat="1" spans="1:11">
       <c r="A37" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B37" s="4">
-        <v>15500</v>
+      <c r="B37" s="2">
+        <v>37540</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>30</v>
@@ -3648,12 +3666,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="38" s="1" customFormat="1" spans="1:11">
       <c r="A38" s="1" t="s">
         <v>67</v>
       </c>
       <c r="B38" s="4">
-        <v>16100</v>
+        <v>39700</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>30</v>
@@ -3683,12 +3701,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="39" s="1" customFormat="1" spans="1:11">
       <c r="A39" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B39" s="4">
-        <v>16800</v>
+      <c r="B39" s="2">
+        <v>41920</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>30</v>
@@ -3718,12 +3736,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="40" s="1" customFormat="1" spans="1:11">
       <c r="A40" s="1" t="s">
         <v>69</v>
       </c>
       <c r="B40" s="4">
-        <v>17400</v>
+        <v>44200</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>30</v>
@@ -3753,12 +3771,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="41" s="1" customFormat="1" spans="1:11">
       <c r="A41" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B41" s="4">
-        <v>18100</v>
+      <c r="B41" s="2">
+        <v>46540</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>30</v>
@@ -3788,12 +3806,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="42" s="1" customFormat="1" spans="1:11">
       <c r="A42" s="1" t="s">
         <v>71</v>
       </c>
       <c r="B42" s="4">
-        <v>18800</v>
+        <v>48940</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>30</v>
@@ -3823,12 +3841,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="43" s="1" customFormat="1" spans="1:11">
       <c r="A43" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B43" s="4">
-        <v>19400</v>
+      <c r="B43" s="2">
+        <v>51400</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>30</v>
@@ -3858,12 +3876,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="44" s="1" customFormat="1" spans="1:11">
       <c r="A44" s="1" t="s">
         <v>73</v>
       </c>
       <c r="B44" s="4">
-        <v>45100</v>
+        <v>53920</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>30</v>
@@ -3893,12 +3911,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="45" s="1" customFormat="1" spans="1:11">
       <c r="A45" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B45" s="4">
-        <v>47300</v>
+      <c r="B45" s="2">
+        <v>56500</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>30</v>
@@ -3928,12 +3946,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="46" s="1" customFormat="1" spans="1:11">
       <c r="A46" s="1" t="s">
         <v>75</v>
       </c>
       <c r="B46" s="4">
-        <v>49500</v>
+        <v>59140</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>30</v>
@@ -3963,12 +3981,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="47" s="1" customFormat="1" spans="1:11">
       <c r="A47" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B47" s="4">
-        <v>51700</v>
+      <c r="B47" s="2">
+        <v>61840</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>30</v>
@@ -3998,12 +4016,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="48" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="48" s="1" customFormat="1" spans="1:11">
       <c r="A48" s="1" t="s">
         <v>77</v>
       </c>
       <c r="B48" s="4">
-        <v>53900</v>
+        <v>64600</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>30</v>
@@ -4033,12 +4051,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="49" s="1" customFormat="1" spans="1:11">
       <c r="A49" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B49" s="4">
-        <v>56100</v>
+      <c r="B49" s="2">
+        <v>67420</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>30</v>
@@ -4068,12 +4086,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="50" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="50" s="1" customFormat="1" spans="1:11">
       <c r="A50" s="1" t="s">
         <v>79</v>
       </c>
       <c r="B50" s="4">
-        <v>58300</v>
+        <v>70300</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>30</v>
@@ -4103,12 +4121,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="51" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="51" s="1" customFormat="1" spans="1:11">
       <c r="A51" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B51" s="4">
-        <v>60500</v>
+      <c r="B51" s="2">
+        <v>73240</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>30</v>
@@ -4138,12 +4156,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="52" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="52" s="1" customFormat="1" spans="1:11">
       <c r="A52" s="1" t="s">
         <v>81</v>
       </c>
       <c r="B52" s="4">
-        <v>62700</v>
+        <v>76240</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>30</v>
@@ -4173,12 +4191,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="53" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="53" s="1" customFormat="1" spans="1:11">
       <c r="A53" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B53" s="4">
-        <v>64900</v>
+      <c r="B53" s="2">
+        <v>79300</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>30</v>
@@ -4208,12 +4226,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="54" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="54" s="1" customFormat="1" spans="1:11">
       <c r="A54" s="1" t="s">
         <v>83</v>
       </c>
       <c r="B54" s="4">
-        <v>66700</v>
+        <v>82420</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>30</v>
@@ -4243,12 +4261,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="55" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="55" s="1" customFormat="1" spans="1:11">
       <c r="A55" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B55" s="4">
-        <v>68200</v>
+      <c r="B55" s="2">
+        <v>85600</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>30</v>
@@ -4278,12 +4296,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="56" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="56" s="1" customFormat="1" spans="1:11">
       <c r="A56" s="1" t="s">
         <v>85</v>
       </c>
       <c r="B56" s="4">
-        <v>69600</v>
+        <v>88840</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>30</v>
@@ -4313,12 +4331,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="57" s="1" customFormat="1" spans="1:11">
       <c r="A57" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B57" s="4">
-        <v>71100</v>
+      <c r="B57" s="2">
+        <v>92140</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>30</v>
@@ -4348,12 +4366,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="58" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="58" s="1" customFormat="1" spans="1:11">
       <c r="A58" s="1" t="s">
         <v>87</v>
       </c>
       <c r="B58" s="4">
-        <v>72600</v>
+        <v>95500</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>30</v>
@@ -4383,12 +4401,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="59" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="59" s="1" customFormat="1" spans="1:11">
       <c r="A59" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B59" s="4">
-        <v>74000</v>
+      <c r="B59" s="2">
+        <v>98920</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>30</v>
@@ -4418,12 +4436,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="60" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="60" s="1" customFormat="1" spans="1:11">
       <c r="A60" s="1" t="s">
         <v>89</v>
       </c>
       <c r="B60" s="4">
-        <v>75500</v>
+        <v>102400</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>30</v>
@@ -4453,12 +4471,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="61" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="61" s="1" customFormat="1" spans="1:11">
       <c r="A61" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B61" s="4">
-        <v>77000</v>
+      <c r="B61" s="2">
+        <v>105940</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>30</v>
@@ -4488,12 +4506,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="62" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="62" s="1" customFormat="1" spans="1:11">
       <c r="A62" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B62" s="4">
-        <v>78000</v>
+        <v>109540</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>30</v>
@@ -4523,12 +4541,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="63" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="63" s="1" customFormat="1" spans="1:11">
       <c r="A63" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B63" s="4">
-        <v>80000</v>
+      <c r="B63" s="2">
+        <v>113200</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>30</v>
@@ -4558,12 +4576,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="64" s="1" customFormat="1" spans="1:11">
       <c r="A64" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B64" s="4">
-        <v>100000</v>
+        <v>116920</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>30</v>
@@ -4593,12 +4611,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="65" s="1" customFormat="1" spans="1:11">
       <c r="A65" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B65" s="4">
-        <v>102000</v>
+      <c r="B65" s="2">
+        <v>120700</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>30</v>
@@ -4628,12 +4646,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="66" s="1" customFormat="1" spans="1:11">
       <c r="A66" s="1" t="s">
         <v>95</v>
       </c>
       <c r="B66" s="4">
-        <v>104000</v>
+        <v>124540</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>30</v>
@@ -4663,12 +4681,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="67" s="1" customFormat="1" spans="1:11">
       <c r="A67" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B67" s="4">
-        <v>107000</v>
+      <c r="B67" s="2">
+        <v>128440</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>30</v>
@@ -4698,12 +4716,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="68" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="68" s="1" customFormat="1" spans="1:11">
       <c r="A68" s="1" t="s">
         <v>97</v>
       </c>
       <c r="B68" s="4">
-        <v>109000</v>
+        <v>132400</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>30</v>
@@ -4733,12 +4751,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="69" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="69" s="1" customFormat="1" spans="1:11">
       <c r="A69" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B69" s="4">
-        <v>111000</v>
+      <c r="B69" s="2">
+        <v>136420</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>30</v>
@@ -4768,12 +4786,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="70" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="70" s="1" customFormat="1" spans="1:11">
       <c r="A70" s="1" t="s">
         <v>99</v>
       </c>
       <c r="B70" s="4">
-        <v>113000</v>
+        <v>140500</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>30</v>
@@ -4803,12 +4821,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="71" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="71" s="1" customFormat="1" spans="1:11">
       <c r="A71" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B71" s="4">
-        <v>115000</v>
+      <c r="B71" s="2">
+        <v>144640</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>30</v>
@@ -4838,12 +4856,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="72" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="72" s="1" customFormat="1" spans="1:11">
       <c r="A72" s="1" t="s">
         <v>101</v>
       </c>
       <c r="B72" s="4">
-        <v>118000</v>
+        <v>148840</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>30</v>
@@ -4873,12 +4891,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="73" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="73" s="1" customFormat="1" spans="1:11">
       <c r="A73" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B73" s="4">
-        <v>120000</v>
+      <c r="B73" s="2">
+        <v>153100</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>30</v>
@@ -4908,12 +4926,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="74" s="1" customFormat="1" spans="1:11">
       <c r="A74" s="1" t="s">
         <v>103</v>
       </c>
       <c r="B74" s="4">
-        <v>961000</v>
+        <v>157420</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>30</v>
@@ -4943,12 +4961,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="75" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="75" s="1" customFormat="1" spans="1:11">
       <c r="A75" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B75" s="4">
-        <v>971000</v>
+      <c r="B75" s="2">
+        <v>161800</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>30</v>
@@ -4978,12 +4996,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="76" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="76" s="1" customFormat="1" spans="1:11">
       <c r="A76" s="1" t="s">
         <v>105</v>
       </c>
       <c r="B76" s="4">
-        <v>981000</v>
+        <v>166240</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>30</v>
@@ -5013,12 +5031,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="77" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="77" s="1" customFormat="1" spans="1:11">
       <c r="A77" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B77" s="4">
-        <v>991000</v>
+      <c r="B77" s="2">
+        <v>170740</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>30</v>
@@ -5048,12 +5066,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="78" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="78" s="1" customFormat="1" spans="1:11">
       <c r="A78" s="1" t="s">
         <v>107</v>
       </c>
       <c r="B78" s="4">
-        <v>1001000</v>
+        <v>175300</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>30</v>
@@ -5083,12 +5101,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="79" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="79" s="1" customFormat="1" spans="1:11">
       <c r="A79" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B79" s="4">
-        <v>1011000</v>
+      <c r="B79" s="2">
+        <v>179920</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>30</v>
@@ -5118,12 +5136,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="80" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="80" s="1" customFormat="1" spans="1:11">
       <c r="A80" s="1" t="s">
         <v>109</v>
       </c>
       <c r="B80" s="4">
-        <v>1021000</v>
+        <v>184600</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>30</v>
@@ -5153,12 +5171,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="81" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="81" s="1" customFormat="1" spans="1:11">
       <c r="A81" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B81" s="4">
-        <v>1031000</v>
+      <c r="B81" s="2">
+        <v>189340</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>30</v>
@@ -5188,12 +5206,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="82" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="82" s="1" customFormat="1" spans="1:11">
       <c r="A82" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B82" s="4">
-        <v>1041000</v>
+        <v>194140</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>30</v>
@@ -5223,12 +5241,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="83" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="83" s="1" customFormat="1" spans="1:11">
       <c r="A83" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B83" s="4">
-        <v>1051000</v>
+      <c r="B83" s="2">
+        <v>199000</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>30</v>
@@ -5258,12 +5276,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="84" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="84" s="1" customFormat="1" spans="1:11">
       <c r="A84" s="1" t="s">
         <v>113</v>
       </c>
       <c r="B84" s="4">
-        <v>1153000</v>
+        <v>203920</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>30</v>
@@ -5293,12 +5311,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="85" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="85" s="1" customFormat="1" spans="1:11">
       <c r="A85" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B85" s="4">
-        <v>1165000</v>
+      <c r="B85" s="2">
+        <v>208900</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>30</v>
@@ -5328,12 +5346,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="86" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="86" s="1" customFormat="1" spans="1:11">
       <c r="A86" s="1" t="s">
         <v>115</v>
       </c>
       <c r="B86" s="4">
-        <v>1177000</v>
+        <v>213940</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>30</v>
@@ -5363,12 +5381,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="87" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="87" s="1" customFormat="1" spans="1:11">
       <c r="A87" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B87" s="4">
-        <v>1189000</v>
+      <c r="B87" s="2">
+        <v>219040</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>30</v>
@@ -5398,12 +5416,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="88" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="88" s="1" customFormat="1" spans="1:11">
       <c r="A88" s="1" t="s">
         <v>117</v>
       </c>
       <c r="B88" s="4">
-        <v>1201000</v>
+        <v>224200</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>30</v>
@@ -5433,12 +5451,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="89" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="89" s="1" customFormat="1" spans="1:11">
       <c r="A89" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B89" s="4">
-        <v>1213000</v>
+      <c r="B89" s="2">
+        <v>229420</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>30</v>
@@ -5468,12 +5486,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="90" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="90" s="1" customFormat="1" spans="1:11">
       <c r="A90" s="1" t="s">
         <v>119</v>
       </c>
       <c r="B90" s="4">
-        <v>1225000</v>
+        <v>234700</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>30</v>
@@ -5503,12 +5521,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="91" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="91" s="1" customFormat="1" spans="1:11">
       <c r="A91" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B91" s="4">
-        <v>1237000</v>
+      <c r="B91" s="2">
+        <v>240040</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>30</v>
@@ -5538,12 +5556,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="92" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="92" s="1" customFormat="1" spans="1:11">
       <c r="A92" s="1" t="s">
         <v>121</v>
       </c>
       <c r="B92" s="4">
-        <v>1249000</v>
+        <v>245440</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>30</v>
@@ -5573,12 +5591,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="93" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="93" s="1" customFormat="1" spans="1:11">
       <c r="A93" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B93" s="4">
-        <v>1262000</v>
+      <c r="B93" s="2">
+        <v>250900</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>30</v>
@@ -5608,12 +5626,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="94" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="94" s="1" customFormat="1" spans="1:11">
       <c r="A94" s="1" t="s">
         <v>123</v>
       </c>
       <c r="B94" s="4">
-        <v>1569000</v>
+        <v>256420</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>30</v>
@@ -5643,12 +5661,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="95" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="95" s="1" customFormat="1" spans="1:11">
       <c r="A95" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B95" s="4">
-        <v>1604000</v>
+      <c r="B95" s="2">
+        <v>262000</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>30</v>
@@ -5678,12 +5696,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="96" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="96" s="1" customFormat="1" spans="1:11">
       <c r="A96" s="1" t="s">
         <v>125</v>
       </c>
       <c r="B96" s="4">
-        <v>1638000</v>
+        <v>267640</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>30</v>
@@ -5713,12 +5731,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="97" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="97" s="1" customFormat="1" spans="1:11">
       <c r="A97" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B97" s="4">
-        <v>1673000</v>
+      <c r="B97" s="2">
+        <v>273340</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>30</v>
@@ -5748,12 +5766,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="98" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="98" s="1" customFormat="1" spans="1:11">
       <c r="A98" s="1" t="s">
         <v>127</v>
       </c>
       <c r="B98" s="4">
-        <v>1707000</v>
+        <v>279100</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>30</v>
@@ -5783,12 +5801,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="99" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="99" s="1" customFormat="1" spans="1:11">
       <c r="A99" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B99" s="4">
-        <v>1742000</v>
+      <c r="B99" s="2">
+        <v>284920</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>30</v>
@@ -5818,12 +5836,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="100" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="100" s="1" customFormat="1" spans="1:11">
       <c r="A100" s="1" t="s">
         <v>129</v>
       </c>
       <c r="B100" s="4">
-        <v>1776000</v>
+        <v>290800</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>30</v>
@@ -5853,12 +5871,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="101" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="101" s="1" customFormat="1" spans="1:11">
       <c r="A101" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B101" s="4">
-        <v>1811000</v>
+      <c r="B101" s="2">
+        <v>296740</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>30</v>
@@ -5888,12 +5906,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="102" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="102" s="1" customFormat="1" spans="1:11">
       <c r="A102" s="1" t="s">
         <v>131</v>
       </c>
       <c r="B102" s="4">
-        <v>1845000</v>
+        <v>302740</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>30</v>
@@ -5923,12 +5941,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="103" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="103" s="1" customFormat="1" spans="1:11">
       <c r="A103" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B103" s="4">
-        <v>1880000</v>
+      <c r="B103" s="2">
+        <v>308800</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>30</v>
@@ -5958,12 +5976,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="104" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="104" s="1" customFormat="1" spans="1:11">
       <c r="A104" s="1" t="s">
         <v>133</v>
       </c>
       <c r="B104" s="4">
-        <v>3140000</v>
+        <v>314920</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>30</v>
@@ -5993,12 +6011,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="105" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="105" s="1" customFormat="1" spans="1:11">
       <c r="A105" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B105" s="4">
-        <v>3210000</v>
+      <c r="B105" s="2">
+        <v>321100</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>30</v>
@@ -6028,12 +6046,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="106" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="106" s="1" customFormat="1" spans="1:11">
       <c r="A106" s="1" t="s">
         <v>135</v>
       </c>
       <c r="B106" s="4">
-        <v>3280000</v>
+        <v>327340</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>30</v>
@@ -6063,12 +6081,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="107" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="107" s="1" customFormat="1" spans="1:11">
       <c r="A107" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B107" s="4">
-        <v>3350000</v>
+      <c r="B107" s="2">
+        <v>333640</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>30</v>
@@ -6098,12 +6116,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="108" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="108" s="1" customFormat="1" spans="1:11">
       <c r="A108" s="1" t="s">
         <v>137</v>
       </c>
       <c r="B108" s="4">
-        <v>3410000</v>
+        <v>340000</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>30</v>
@@ -6133,12 +6151,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="109" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="109" s="1" customFormat="1" spans="1:11">
       <c r="A109" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B109" s="4">
-        <v>3480000</v>
+      <c r="B109" s="2">
+        <v>346420</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>30</v>
@@ -6168,12 +6186,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="110" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="110" s="1" customFormat="1" spans="1:11">
       <c r="A110" s="1" t="s">
         <v>139</v>
       </c>
       <c r="B110" s="4">
-        <v>3550000</v>
+        <v>352900</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>30</v>
@@ -6203,12 +6221,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="111" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="111" s="1" customFormat="1" spans="1:11">
       <c r="A111" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B111" s="4">
-        <v>3620000</v>
+      <c r="B111" s="2">
+        <v>359440</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>30</v>
@@ -6238,12 +6256,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="112" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="112" s="1" customFormat="1" spans="1:11">
       <c r="A112" s="1" t="s">
         <v>141</v>
       </c>
       <c r="B112" s="4">
-        <v>3690000</v>
+        <v>366040</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>30</v>
@@ -6273,12 +6291,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="113" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="113" s="1" customFormat="1" spans="1:11">
       <c r="A113" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B113" s="4">
-        <v>3760000</v>
+      <c r="B113" s="2">
+        <v>372700</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>30</v>
@@ -6308,12 +6326,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="114" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="114" s="1" customFormat="1" spans="1:11">
       <c r="A114" s="1" t="s">
         <v>143</v>
       </c>
       <c r="B114" s="4">
-        <v>4710000</v>
+        <v>379420</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>30</v>
@@ -6343,12 +6361,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="115" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="115" s="1" customFormat="1" spans="1:11">
       <c r="A115" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B115" s="4">
-        <v>4810000</v>
+      <c r="B115" s="2">
+        <v>386200</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>30</v>
@@ -6378,12 +6396,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="116" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="116" s="1" customFormat="1" spans="1:11">
       <c r="A116" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B116" s="4">
-        <v>4920000</v>
+        <v>393040</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>30</v>
@@ -6413,12 +6431,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="117" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="117" s="1" customFormat="1" spans="1:11">
       <c r="A117" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B117" s="4">
-        <v>5020000</v>
+      <c r="B117" s="2">
+        <v>399940</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>30</v>
@@ -6448,12 +6466,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="118" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="118" s="1" customFormat="1" spans="1:11">
       <c r="A118" s="1" t="s">
         <v>147</v>
       </c>
       <c r="B118" s="4">
-        <v>5120000</v>
+        <v>406900</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>30</v>
@@ -6483,12 +6501,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="119" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="119" s="1" customFormat="1" spans="1:11">
       <c r="A119" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B119" s="4">
-        <v>5230000</v>
+      <c r="B119" s="2">
+        <v>413920</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>30</v>
@@ -6518,12 +6536,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="120" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="120" s="1" customFormat="1" spans="1:11">
       <c r="A120" s="1" t="s">
         <v>149</v>
       </c>
       <c r="B120" s="4">
-        <v>5330000</v>
+        <v>421000</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>30</v>
@@ -6553,12 +6571,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="121" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="121" s="1" customFormat="1" spans="1:11">
       <c r="A121" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B121" s="4">
-        <v>5430000</v>
+      <c r="B121" s="2">
+        <v>428140</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>30</v>
@@ -6588,12 +6606,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="122" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="122" s="1" customFormat="1" spans="1:11">
       <c r="A122" s="1" t="s">
         <v>151</v>
       </c>
       <c r="B122" s="4">
-        <v>5540000</v>
+        <v>435340</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>30</v>
@@ -6623,12 +6641,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="123" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="123" s="1" customFormat="1" spans="1:11">
       <c r="A123" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B123" s="4">
-        <v>5640000</v>
+      <c r="B123" s="2">
+        <v>442600</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>30</v>
@@ -6658,12 +6676,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="124" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="124" s="1" customFormat="1" spans="1:11">
       <c r="A124" s="1" t="s">
         <v>153</v>
       </c>
       <c r="B124" s="4">
-        <v>9420000</v>
+        <v>449920</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>30</v>
@@ -6693,12 +6711,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="125" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="125" s="1" customFormat="1" spans="1:11">
       <c r="A125" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B125" s="4">
-        <v>9620000</v>
+      <c r="B125" s="2">
+        <v>457300</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>30</v>
@@ -6728,12 +6746,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="126" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="126" s="1" customFormat="1" spans="1:11">
       <c r="A126" s="1" t="s">
         <v>155</v>
       </c>
       <c r="B126" s="4">
-        <v>9830000</v>
+        <v>464740</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>30</v>
@@ -6763,12 +6781,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="127" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="127" s="1" customFormat="1" spans="1:11">
       <c r="A127" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B127" s="4">
-        <v>10040000</v>
+      <c r="B127" s="2">
+        <v>472240</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>30</v>
@@ -6798,12 +6816,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="128" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="128" s="1" customFormat="1" spans="1:11">
       <c r="A128" s="1" t="s">
         <v>157</v>
       </c>
       <c r="B128" s="4">
-        <v>10240000</v>
+        <v>479800</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>30</v>
@@ -6833,12 +6851,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="129" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="129" s="1" customFormat="1" spans="1:11">
       <c r="A129" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B129" s="4">
-        <v>10450000</v>
+      <c r="B129" s="2">
+        <v>487420</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>30</v>
@@ -6868,12 +6886,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="130" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="130" s="1" customFormat="1" spans="1:11">
       <c r="A130" s="1" t="s">
         <v>159</v>
       </c>
       <c r="B130" s="4">
-        <v>10660000</v>
+        <v>495100</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>30</v>
@@ -6903,12 +6921,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="131" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="131" s="1" customFormat="1" spans="1:11">
       <c r="A131" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B131" s="4">
-        <v>10860000</v>
+      <c r="B131" s="2">
+        <v>502840</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>30</v>
@@ -6938,12 +6956,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="132" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="132" s="1" customFormat="1" spans="1:11">
       <c r="A132" s="1" t="s">
         <v>161</v>
       </c>
       <c r="B132" s="4">
-        <v>11070000</v>
+        <v>510640</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>30</v>
@@ -6973,12 +6991,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="133" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="133" s="1" customFormat="1" spans="1:11">
       <c r="A133" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B133" s="4">
-        <v>11280000</v>
+      <c r="B133" s="2">
+        <v>518500</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>30</v>
@@ -7008,12 +7026,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="134" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="134" s="1" customFormat="1" spans="1:11">
       <c r="A134" s="1" t="s">
         <v>163</v>
       </c>
       <c r="B134" s="4">
-        <v>48300000</v>
+        <v>526420</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>30</v>
@@ -7043,12 +7061,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="135" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="135" s="1" customFormat="1" spans="1:11">
       <c r="A135" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B135" s="4">
-        <v>49400000</v>
+      <c r="B135" s="2">
+        <v>534400</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>30</v>
@@ -7078,12 +7096,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="136" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="136" s="1" customFormat="1" spans="1:11">
       <c r="A136" s="1" t="s">
         <v>165</v>
       </c>
       <c r="B136" s="4">
-        <v>50400000</v>
+        <v>542440</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>30</v>
@@ -7113,12 +7131,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="137" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="137" s="1" customFormat="1" spans="1:11">
       <c r="A137" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B137" s="4">
-        <v>51500000</v>
+      <c r="B137" s="2">
+        <v>550540</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>30</v>
@@ -7148,12 +7166,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="138" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="138" s="1" customFormat="1" spans="1:11">
       <c r="A138" s="1" t="s">
         <v>167</v>
       </c>
       <c r="B138" s="4">
-        <v>52500000</v>
+        <v>558700</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>30</v>
@@ -7183,12 +7201,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="139" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="139" s="1" customFormat="1" spans="1:11">
       <c r="A139" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B139" s="4">
-        <v>53600000</v>
+      <c r="B139" s="2">
+        <v>566920</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>30</v>
@@ -7218,12 +7236,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="140" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="140" s="1" customFormat="1" spans="1:11">
       <c r="A140" s="1" t="s">
         <v>169</v>
       </c>
       <c r="B140" s="4">
-        <v>54700000</v>
+        <v>575200</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>30</v>
@@ -7253,12 +7271,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="141" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="141" s="1" customFormat="1" spans="1:11">
       <c r="A141" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B141" s="4">
-        <v>55700000</v>
+      <c r="B141" s="2">
+        <v>583540</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>30</v>
@@ -7288,12 +7306,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="142" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="142" s="1" customFormat="1" spans="1:11">
       <c r="A142" s="1" t="s">
         <v>171</v>
       </c>
       <c r="B142" s="4">
-        <v>56800000</v>
+        <v>591940</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>30</v>
@@ -7323,12 +7341,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="143" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="143" s="1" customFormat="1" spans="1:11">
       <c r="A143" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B143" s="4">
-        <v>57800000</v>
+      <c r="B143" s="2">
+        <v>600400</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>30</v>
@@ -7358,12 +7376,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="144" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="144" s="1" customFormat="1" spans="1:11">
       <c r="A144" s="1" t="s">
         <v>173</v>
       </c>
       <c r="B144" s="4">
-        <v>60800000</v>
+        <v>608920</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>30</v>
@@ -7393,12 +7411,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="145" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="145" s="1" customFormat="1" spans="1:11">
       <c r="A145" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B145" s="4">
-        <v>61500000</v>
+      <c r="B145" s="2">
+        <v>617500</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>30</v>
@@ -7428,12 +7446,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="146" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="146" s="1" customFormat="1" spans="1:11">
       <c r="A146" s="1" t="s">
         <v>175</v>
       </c>
       <c r="B146" s="4">
-        <v>62100000</v>
+        <v>626140</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>30</v>
@@ -7463,12 +7481,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="147" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="147" s="1" customFormat="1" spans="1:11">
       <c r="A147" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B147" s="4">
-        <v>62700000</v>
+      <c r="B147" s="2">
+        <v>634840</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>30</v>
@@ -7498,12 +7516,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="148" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="148" s="1" customFormat="1" spans="1:11">
       <c r="A148" s="1" t="s">
         <v>177</v>
       </c>
       <c r="B148" s="4">
-        <v>63400000</v>
+        <v>643600</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>30</v>
@@ -7533,12 +7551,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="149" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="149" s="1" customFormat="1" spans="1:11">
       <c r="A149" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B149" s="4">
-        <v>64000000</v>
+      <c r="B149" s="2">
+        <v>652420</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>30</v>
@@ -7568,12 +7586,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="150" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="150" s="1" customFormat="1" spans="1:11">
       <c r="A150" s="1" t="s">
         <v>179</v>
       </c>
       <c r="B150" s="4">
-        <v>64600000</v>
+        <v>661300</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>30</v>
@@ -7603,12 +7621,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="151" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="151" s="1" customFormat="1" spans="1:11">
       <c r="A151" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B151" s="4">
-        <v>65300000</v>
+      <c r="B151" s="2">
+        <v>670240</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>30</v>
@@ -7638,12 +7656,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="152" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="152" s="1" customFormat="1" spans="1:11">
       <c r="A152" s="1" t="s">
         <v>181</v>
       </c>
       <c r="B152" s="4">
-        <v>65900000</v>
+        <v>679240</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>30</v>
@@ -7673,12 +7691,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="153" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="153" s="1" customFormat="1" spans="1:11">
       <c r="A153" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B153" s="4">
-        <v>66600000</v>
+      <c r="B153" s="2">
+        <v>688300</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>30</v>
@@ -7708,12 +7726,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="154" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="154" s="1" customFormat="1" spans="1:11">
       <c r="A154" s="1" t="s">
         <v>183</v>
       </c>
       <c r="B154" s="4">
-        <v>71000000</v>
+        <v>697420</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>30</v>
@@ -7743,12 +7761,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="155" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="155" s="1" customFormat="1" spans="1:11">
       <c r="A155" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B155" s="4">
-        <v>71700000</v>
+      <c r="B155" s="2">
+        <v>2100000</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>30</v>
@@ -7778,12 +7796,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="156" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="156" s="1" customFormat="1" spans="1:11">
       <c r="A156" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B156" s="4">
-        <v>72400000</v>
+      <c r="B156" s="2">
+        <v>2100000</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>30</v>
@@ -7813,12 +7831,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="157" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="157" s="1" customFormat="1" spans="1:11">
       <c r="A157" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B157" s="4">
-        <v>73200000</v>
+      <c r="B157" s="2">
+        <v>2100000</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>30</v>
@@ -7848,12 +7866,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="158" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="158" s="1" customFormat="1" spans="1:11">
       <c r="A158" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="B158" s="4">
-        <v>73900000</v>
+      <c r="B158" s="2">
+        <v>2100000</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>30</v>
@@ -7883,12 +7901,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="159" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="159" s="1" customFormat="1" spans="1:11">
       <c r="A159" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B159" s="4">
-        <v>74700000</v>
+      <c r="B159" s="2">
+        <v>2100000</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>30</v>
@@ -7918,12 +7936,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="160" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="160" s="1" customFormat="1" spans="1:11">
       <c r="A160" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B160" s="4">
-        <v>75400000</v>
+      <c r="B160" s="2">
+        <v>2100000</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>30</v>
@@ -7953,12 +7971,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="161" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="161" s="1" customFormat="1" spans="1:11">
       <c r="A161" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B161" s="4">
-        <v>76200000</v>
+      <c r="B161" s="2">
+        <v>2100000</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>30</v>
@@ -7988,12 +8006,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="162" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="162" s="1" customFormat="1" spans="1:11">
       <c r="A162" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B162" s="4">
-        <v>76900000</v>
+      <c r="B162" s="2">
+        <v>2100000</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>30</v>
@@ -8023,12 +8041,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="163" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="163" s="1" customFormat="1" spans="1:11">
       <c r="A163" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B163" s="4">
-        <v>77600000</v>
+      <c r="B163" s="2">
+        <v>2100000</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>30</v>
@@ -8058,12 +8076,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="164" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="164" s="1" customFormat="1" spans="1:11">
       <c r="A164" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B164" s="4">
-        <v>81100000</v>
+      <c r="B164" s="2">
+        <v>2100000</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>30</v>
@@ -8093,12 +8111,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="165" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="165" s="1" customFormat="1" spans="1:11">
       <c r="A165" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B165" s="4">
-        <v>81900000</v>
+      <c r="B165" s="2">
+        <v>2300000</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>30</v>
@@ -8128,12 +8146,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="166" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="166" s="1" customFormat="1" spans="1:11">
       <c r="A166" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B166" s="4">
-        <v>82800000</v>
+      <c r="B166" s="2">
+        <v>2300000</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>30</v>
@@ -8163,12 +8181,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="167" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="167" s="1" customFormat="1" spans="1:11">
       <c r="A167" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B167" s="4">
-        <v>83600000</v>
+      <c r="B167" s="2">
+        <v>2300000</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>30</v>
@@ -8198,12 +8216,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="168" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="168" s="1" customFormat="1" spans="1:11">
       <c r="A168" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B168" s="4">
-        <v>84500000</v>
+      <c r="B168" s="2">
+        <v>2300000</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>30</v>
@@ -8233,12 +8251,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="169" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="169" s="1" customFormat="1" spans="1:11">
       <c r="A169" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B169" s="4">
-        <v>85300000</v>
+      <c r="B169" s="2">
+        <v>2300000</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>30</v>
@@ -8268,12 +8286,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="170" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="170" s="1" customFormat="1" spans="1:11">
       <c r="A170" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B170" s="4">
-        <v>86200000</v>
+      <c r="B170" s="2">
+        <v>2300000</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>30</v>
@@ -8303,12 +8321,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="171" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="171" s="1" customFormat="1" spans="1:11">
       <c r="A171" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B171" s="4">
-        <v>87000000</v>
+      <c r="B171" s="2">
+        <v>2300000</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>30</v>
@@ -8338,12 +8356,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="172" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="172" s="1" customFormat="1" spans="1:11">
       <c r="A172" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B172" s="4">
-        <v>87900000</v>
+      <c r="B172" s="2">
+        <v>2300000</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>30</v>
@@ -8373,12 +8391,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="173" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="173" s="1" customFormat="1" spans="1:11">
       <c r="A173" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B173" s="4">
-        <v>88700000</v>
+      <c r="B173" s="2">
+        <v>2300000</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>30</v>
@@ -8408,12 +8426,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="174" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="174" s="1" customFormat="1" spans="1:11">
       <c r="A174" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B174" s="4">
-        <v>250800000</v>
+      <c r="B174" s="2">
+        <v>2300000</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>30</v>
@@ -8443,12 +8461,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="175" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="175" s="1" customFormat="1" spans="1:11">
       <c r="A175" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B175" s="4">
-        <v>253400000</v>
+      <c r="B175" s="2">
+        <v>2500000</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>30</v>
@@ -8478,12 +8496,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="176" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="176" s="1" customFormat="1" spans="1:11">
       <c r="A176" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B176" s="4">
-        <v>256000000</v>
+      <c r="B176" s="2">
+        <v>2500000</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>30</v>
@@ -8513,12 +8531,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="177" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="177" s="1" customFormat="1" spans="1:11">
       <c r="A177" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B177" s="4">
-        <v>258600000</v>
+      <c r="B177" s="2">
+        <v>2500000</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>30</v>
@@ -8548,12 +8566,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="178" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="178" s="1" customFormat="1" spans="1:11">
       <c r="A178" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B178" s="4">
-        <v>261300000</v>
+      <c r="B178" s="2">
+        <v>2500000</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>30</v>
@@ -8583,12 +8601,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="179" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="179" s="1" customFormat="1" spans="1:11">
       <c r="A179" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B179" s="4">
-        <v>263900000</v>
+      <c r="B179" s="2">
+        <v>2500000</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>30</v>
@@ -8618,12 +8636,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="180" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="180" s="1" customFormat="1" spans="1:11">
       <c r="A180" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B180" s="4">
-        <v>266500000</v>
+      <c r="B180" s="2">
+        <v>2500000</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>30</v>
@@ -8653,12 +8671,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="181" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="181" s="1" customFormat="1" spans="1:11">
       <c r="A181" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B181" s="4">
-        <v>269100000</v>
+      <c r="B181" s="2">
+        <v>2500000</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>30</v>
@@ -8688,12 +8706,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="182" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="182" s="1" customFormat="1" spans="1:11">
       <c r="A182" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B182" s="4">
-        <v>271800000</v>
+      <c r="B182" s="2">
+        <v>2500000</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>30</v>
@@ -8723,12 +8741,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="183" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="183" s="1" customFormat="1" spans="1:11">
       <c r="A183" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B183" s="4">
-        <v>274400000</v>
+      <c r="B183" s="2">
+        <v>2500000</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>30</v>
@@ -8758,12 +8776,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="184" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="184" s="1" customFormat="1" spans="1:11">
       <c r="A184" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="B184" s="4">
-        <v>278600000</v>
+      <c r="B184" s="2">
+        <v>2500000</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>30</v>
@@ -8793,12 +8811,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="185" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="185" s="1" customFormat="1" spans="1:11">
       <c r="A185" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B185" s="4">
-        <v>281500000</v>
+      <c r="B185" s="2">
+        <v>3009900</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>30</v>
@@ -8828,12 +8846,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="186" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="186" s="1" customFormat="1" spans="1:11">
       <c r="A186" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B186" s="4">
-        <v>284500000</v>
+      <c r="B186" s="2">
+        <v>3009900</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>30</v>
@@ -8863,12 +8881,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="187" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="187" s="1" customFormat="1" spans="1:11">
       <c r="A187" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B187" s="4">
-        <v>287400000</v>
+      <c r="B187" s="2">
+        <v>3009900</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>30</v>
@@ -8898,12 +8916,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="188" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="188" s="1" customFormat="1" spans="1:11">
       <c r="A188" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="B188" s="4">
-        <v>290300000</v>
+      <c r="B188" s="2">
+        <v>3009900</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>30</v>
@@ -8933,12 +8951,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="189" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="189" s="1" customFormat="1" spans="1:11">
       <c r="A189" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B189" s="4">
-        <v>293200000</v>
+      <c r="B189" s="2">
+        <v>3009900</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>30</v>
@@ -8968,12 +8986,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="190" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="190" s="1" customFormat="1" spans="1:11">
       <c r="A190" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="B190" s="4">
-        <v>296100000</v>
+      <c r="B190" s="2">
+        <v>3009900</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>30</v>
@@ -9003,12 +9021,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="191" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="191" s="1" customFormat="1" spans="1:11">
       <c r="A191" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B191" s="4">
-        <v>299000000</v>
+      <c r="B191" s="2">
+        <v>3009900</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>30</v>
@@ -9038,12 +9056,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="192" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="192" s="1" customFormat="1" spans="1:11">
       <c r="A192" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B192" s="4">
-        <v>302000000</v>
+      <c r="B192" s="2">
+        <v>3009900</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>30</v>
@@ -9073,12 +9091,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="193" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="193" s="1" customFormat="1" spans="1:11">
       <c r="A193" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B193" s="4">
-        <v>304900000</v>
+      <c r="B193" s="2">
+        <v>3009900</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>30</v>
@@ -9108,12 +9126,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="194" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="194" s="1" customFormat="1" spans="1:11">
       <c r="A194" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="B194" s="4">
-        <v>312300000</v>
+      <c r="B194" s="2">
+        <v>3009900</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>30</v>
@@ -9143,12 +9161,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="195" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="195" s="1" customFormat="1" spans="1:11">
       <c r="A195" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B195" s="4">
-        <v>314200000</v>
+      <c r="B195" s="2">
+        <v>3009900</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>30</v>
@@ -9178,12 +9196,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="196" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="196" s="1" customFormat="1" spans="1:11">
       <c r="A196" s="1" t="s">
         <v>225</v>
       </c>
       <c r="B196" s="4">
-        <v>316100000</v>
+        <v>3134640</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>30</v>
@@ -9213,12 +9231,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="197" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="197" s="1" customFormat="1" spans="1:11">
       <c r="A197" s="1" t="s">
         <v>226</v>
       </c>
       <c r="B197" s="4">
-        <v>318000000</v>
+        <v>3134640</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>30</v>
@@ -9248,12 +9266,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="198" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="198" s="1" customFormat="1" spans="1:11">
       <c r="A198" s="1" t="s">
         <v>227</v>
       </c>
       <c r="B198" s="4">
-        <v>320000000</v>
+        <v>3134640</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>30</v>
@@ -9283,12 +9301,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="199" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="199" s="1" customFormat="1" spans="1:11">
       <c r="A199" s="1" t="s">
         <v>228</v>
       </c>
       <c r="B199" s="4">
-        <v>321900000</v>
+        <v>3134640</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>30</v>
@@ -9318,12 +9336,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="200" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="200" s="1" customFormat="1" spans="1:11">
       <c r="A200" s="1" t="s">
         <v>229</v>
       </c>
       <c r="B200" s="4">
-        <v>323800000</v>
+        <v>3134640</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>30</v>
@@ -9353,12 +9371,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="201" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="201" s="1" customFormat="1" spans="1:11">
       <c r="A201" s="1" t="s">
         <v>230</v>
       </c>
       <c r="B201" s="4">
-        <v>325700000</v>
+        <v>3134640</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>30</v>
@@ -9388,12 +9406,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="202" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="202" s="1" customFormat="1" spans="1:11">
       <c r="A202" s="1" t="s">
         <v>231</v>
       </c>
       <c r="B202" s="4">
-        <v>327700000</v>
+        <v>3205740</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>30</v>
@@ -9423,12 +9441,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="203" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="203" s="1" customFormat="1" spans="1:11">
       <c r="A203" s="1" t="s">
         <v>232</v>
       </c>
       <c r="B203" s="4">
-        <v>329600000</v>
+        <v>3205740</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>30</v>
@@ -9458,12 +9476,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="204" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="204" s="1" customFormat="1" spans="1:11">
       <c r="A204" s="1" t="s">
         <v>233</v>
       </c>
       <c r="B204" s="4">
-        <v>340700000</v>
+        <v>3205740</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>30</v>
@@ -9493,12 +9511,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="205" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="205" s="1" customFormat="1" spans="1:11">
       <c r="A205" s="1" t="s">
         <v>234</v>
       </c>
       <c r="B205" s="4">
-        <v>342800000</v>
+        <v>3205740</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>30</v>
@@ -9528,12 +9546,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="206" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="206" s="1" customFormat="1" spans="1:11">
       <c r="A206" s="1" t="s">
         <v>235</v>
       </c>
       <c r="B206" s="4">
-        <v>344900000</v>
+        <v>3205740</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>30</v>
@@ -9563,12 +9581,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="207" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="207" s="1" customFormat="1" spans="1:11">
       <c r="A207" s="1" t="s">
         <v>236</v>
       </c>
       <c r="B207" s="4">
-        <v>347000000</v>
+        <v>3205740</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>30</v>
@@ -9598,12 +9616,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="208" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="208" s="1" customFormat="1" spans="1:11">
       <c r="A208" s="1" t="s">
         <v>237</v>
       </c>
       <c r="B208" s="4">
-        <v>349100000</v>
+        <v>3205740</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>30</v>
@@ -9633,12 +9651,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="209" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="209" s="1" customFormat="1" spans="1:11">
       <c r="A209" s="1" t="s">
         <v>238</v>
       </c>
       <c r="B209" s="4">
-        <v>351200000</v>
+        <v>3205740</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>30</v>
@@ -9668,12 +9686,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="210" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="210" s="1" customFormat="1" spans="1:11">
       <c r="A210" s="1" t="s">
         <v>239</v>
       </c>
       <c r="B210" s="4">
-        <v>353300000</v>
+        <v>3303900</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>30</v>
@@ -9703,12 +9721,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="211" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="211" s="1" customFormat="1" spans="1:11">
       <c r="A211" s="1" t="s">
         <v>240</v>
       </c>
       <c r="B211" s="4">
-        <v>355400000</v>
+        <v>3303900</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>30</v>
@@ -9738,12 +9756,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="212" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="212" s="1" customFormat="1" spans="1:11">
       <c r="A212" s="1" t="s">
         <v>241</v>
       </c>
       <c r="B212" s="4">
-        <v>357500000</v>
+        <v>3303900</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>30</v>
@@ -9773,12 +9791,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="213" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="213" s="1" customFormat="1" spans="1:11">
       <c r="A213" s="1" t="s">
         <v>242</v>
       </c>
       <c r="B213" s="4">
-        <v>359600000</v>
+        <v>3303900</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>30</v>
@@ -9808,12 +9826,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="214" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="214" s="1" customFormat="1" spans="1:11">
       <c r="A214" s="1" t="s">
         <v>243</v>
       </c>
       <c r="B214" s="4">
-        <v>789000000</v>
+        <v>3303900</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>30</v>
@@ -9843,12 +9861,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="215" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="215" s="1" customFormat="1" spans="1:11">
       <c r="A215" s="1" t="s">
         <v>244</v>
       </c>
       <c r="B215" s="4">
-        <v>794000000</v>
+        <v>3303900</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>30</v>
@@ -9878,12 +9896,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="216" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="216" s="1" customFormat="1" spans="1:11">
       <c r="A216" s="1" t="s">
         <v>245</v>
       </c>
       <c r="B216" s="4">
-        <v>799000000</v>
+        <v>3303900</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>30</v>
@@ -9913,12 +9931,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="217" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="217" s="1" customFormat="1" spans="1:11">
       <c r="A217" s="1" t="s">
         <v>246</v>
       </c>
       <c r="B217" s="4">
-        <v>804000000</v>
+        <v>3303900</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>30</v>
@@ -9948,12 +9966,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="218" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="218" s="1" customFormat="1" spans="1:11">
       <c r="A218" s="1" t="s">
         <v>247</v>
       </c>
       <c r="B218" s="4">
-        <v>809000000</v>
+        <v>3303900</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>30</v>
@@ -9983,12 +10001,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="219" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="219" s="1" customFormat="1" spans="1:11">
       <c r="A219" s="1" t="s">
         <v>248</v>
       </c>
       <c r="B219" s="4">
-        <v>814000000</v>
+        <v>3303900</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>30</v>
@@ -10018,12 +10036,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="220" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="220" s="1" customFormat="1" spans="1:11">
       <c r="A220" s="1" t="s">
         <v>249</v>
       </c>
       <c r="B220" s="4">
-        <v>819000000</v>
+        <v>3303900</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>30</v>
@@ -10053,12 +10071,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="221" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="221" s="1" customFormat="1" spans="1:11">
       <c r="A221" s="1" t="s">
         <v>250</v>
       </c>
       <c r="B221" s="4">
-        <v>823000000</v>
+        <v>3303900</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>30</v>
@@ -10088,12 +10106,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="222" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="222" s="1" customFormat="1" spans="1:11">
       <c r="A222" s="1" t="s">
         <v>251</v>
       </c>
       <c r="B222" s="4">
-        <v>828000000</v>
+        <v>3458340</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>30</v>
@@ -10123,12 +10141,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="223" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="223" s="1" customFormat="1" spans="1:11">
       <c r="A223" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B223" s="4">
-        <v>833000000</v>
+      <c r="B223" s="2">
+        <v>3471600</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>30</v>
@@ -10158,12 +10176,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="224" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="224" s="1" customFormat="1" spans="1:11">
       <c r="A224" s="1" t="s">
         <v>253</v>
       </c>
       <c r="B224" s="4">
-        <v>850000000</v>
+        <v>3484920</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>30</v>
@@ -10193,15 +10211,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="225" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="225" s="1" customFormat="1" spans="1:11">
       <c r="A225" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B225" s="4">
-        <v>855000000</v>
+      <c r="B225" s="2">
+        <v>3498300</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D225" s="3" t="s">
         <v>31</v>
@@ -10228,16 +10246,16 @@
         <v>32</v>
       </c>
     </row>
-    <row r="226" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="226" s="1" customFormat="1" spans="1:11">
       <c r="A226" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B226" s="4">
+        <v>3511740</v>
+      </c>
+      <c r="C226" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B226" s="4">
-        <v>861000000</v>
-      </c>
-      <c r="C226" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="D226" s="3" t="s">
         <v>31</v>
       </c>
@@ -10263,15 +10281,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="227" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="227" s="1" customFormat="1" spans="1:11">
       <c r="A227" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B227" s="4">
-        <v>866000000</v>
+        <v>257</v>
+      </c>
+      <c r="B227" s="2">
+        <v>3525240</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D227" s="3" t="s">
         <v>31</v>
@@ -10298,15 +10316,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="228" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="228" s="1" customFormat="1" spans="1:11">
       <c r="A228" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B228" s="4">
-        <v>871000000</v>
+        <v>3538800</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D228" s="3" t="s">
         <v>31</v>
@@ -10333,15 +10351,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="229" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="229" s="1" customFormat="1" spans="1:11">
       <c r="A229" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B229" s="4">
-        <v>876000000</v>
+        <v>3558800</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D229" s="3" t="s">
         <v>31</v>
@@ -10368,15 +10386,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="230" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="230" s="1" customFormat="1" spans="1:11">
       <c r="A230" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B230" s="4">
-        <v>881000000</v>
+        <v>3566100</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D230" s="3" t="s">
         <v>31</v>
@@ -10403,15 +10421,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="231" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="231" s="1" customFormat="1" spans="1:11">
       <c r="A231" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="B231" s="4">
-        <v>887000000</v>
+        <v>261</v>
+      </c>
+      <c r="B231" s="2">
+        <v>3579840</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D231" s="3" t="s">
         <v>31</v>
@@ -10438,15 +10456,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="232" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="232" s="1" customFormat="1" spans="1:11">
       <c r="A232" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B232" s="4">
-        <v>892000000</v>
+        <v>3593640</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D232" s="3" t="s">
         <v>31</v>
@@ -10473,15 +10491,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="233" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="233" s="1" customFormat="1" spans="1:11">
       <c r="A233" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="B233" s="4">
-        <v>897000000</v>
+        <v>263</v>
+      </c>
+      <c r="B233" s="2">
+        <v>3607500</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D233" s="3" t="s">
         <v>31</v>
@@ -10508,15 +10526,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="234" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="234" s="1" customFormat="1" spans="1:11">
       <c r="A234" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B234" s="4">
-        <v>911000000</v>
+        <v>3621420</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D234" s="3" t="s">
         <v>31</v>
@@ -10543,15 +10561,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="235" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="235" s="1" customFormat="1" spans="1:11">
       <c r="A235" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B235" s="4">
-        <v>916000000</v>
+        <v>265</v>
+      </c>
+      <c r="B235" s="2">
+        <v>3635400</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D235" s="3" t="s">
         <v>31</v>
@@ -10578,15 +10596,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="236" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="236" s="1" customFormat="1" spans="1:11">
       <c r="A236" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B236" s="4">
-        <v>922000000</v>
+        <v>3649440</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D236" s="3" t="s">
         <v>31</v>
@@ -10613,15 +10631,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="237" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="237" s="1" customFormat="1" spans="1:11">
       <c r="A237" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="B237" s="4">
-        <v>928000000</v>
+        <v>267</v>
+      </c>
+      <c r="B237" s="2">
+        <v>3663540</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D237" s="3" t="s">
         <v>31</v>
@@ -10648,15 +10666,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="238" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="238" s="1" customFormat="1" spans="1:11">
       <c r="A238" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B238" s="4">
-        <v>933000000</v>
+        <v>3677700</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D238" s="3" t="s">
         <v>31</v>
@@ -10683,15 +10701,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="239" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="239" s="1" customFormat="1" spans="1:11">
       <c r="A239" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="B239" s="4">
-        <v>939000000</v>
+        <v>269</v>
+      </c>
+      <c r="B239" s="2">
+        <v>3691920</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D239" s="3" t="s">
         <v>31</v>
@@ -10718,15 +10736,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="240" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="240" s="1" customFormat="1" spans="1:11">
       <c r="A240" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B240" s="4">
-        <v>944000000</v>
+        <v>3706200</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D240" s="3" t="s">
         <v>31</v>
@@ -10753,15 +10771,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="241" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="241" s="1" customFormat="1" spans="1:11">
       <c r="A241" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="B241" s="4">
-        <v>950000000</v>
+        <v>271</v>
+      </c>
+      <c r="B241" s="2">
+        <v>3720540</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D241" s="3" t="s">
         <v>31</v>
@@ -10788,15 +10806,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="242" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="242" s="1" customFormat="1" spans="1:11">
       <c r="A242" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B242" s="4">
-        <v>956000000</v>
+        <v>3734940</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D242" s="3" t="s">
         <v>31</v>
@@ -10823,15 +10841,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="243" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="243" s="1" customFormat="1" spans="1:11">
       <c r="A243" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="B243" s="4">
-        <v>961000000</v>
+        <v>273</v>
+      </c>
+      <c r="B243" s="2">
+        <v>3749400</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D243" s="3" t="s">
         <v>31</v>
@@ -10858,15 +10876,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="244" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="244" s="1" customFormat="1" spans="1:11">
       <c r="A244" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B244" s="4">
-        <v>971000000</v>
+        <v>3763920</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D244" s="3" t="s">
         <v>31</v>
@@ -10893,15 +10911,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="245" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="245" s="1" customFormat="1" spans="1:11">
       <c r="A245" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="B245" s="4">
-        <v>977000000</v>
+        <v>275</v>
+      </c>
+      <c r="B245" s="2">
+        <v>3778500</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D245" s="3" t="s">
         <v>31</v>
@@ -10928,15 +10946,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="246" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="246" s="1" customFormat="1" spans="1:11">
       <c r="A246" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B246" s="4">
-        <v>983000000</v>
+        <v>3793140</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D246" s="3" t="s">
         <v>31</v>
@@ -10963,15 +10981,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="247" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="247" s="1" customFormat="1" spans="1:11">
       <c r="A247" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="B247" s="4">
-        <v>989000000</v>
+        <v>277</v>
+      </c>
+      <c r="B247" s="2">
+        <v>3807840</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D247" s="3" t="s">
         <v>31</v>
@@ -10998,15 +11016,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="248" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="248" s="1" customFormat="1" spans="1:11">
       <c r="A248" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B248" s="4">
-        <v>995000000</v>
+        <v>3822600</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D248" s="3" t="s">
         <v>31</v>
@@ -11033,15 +11051,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="249" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="249" s="1" customFormat="1" spans="1:11">
       <c r="A249" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="B249" s="4">
-        <v>1001000000</v>
+        <v>279</v>
+      </c>
+      <c r="B249" s="2">
+        <v>3837420</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D249" s="3" t="s">
         <v>31</v>
@@ -11068,15 +11086,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="250" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="250" s="1" customFormat="1" spans="1:11">
       <c r="A250" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B250" s="4">
-        <v>1007000000</v>
+        <v>3852300</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D250" s="3" t="s">
         <v>31</v>
@@ -11103,15 +11121,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="251" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="251" s="1" customFormat="1" spans="1:11">
       <c r="A251" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B251" s="4">
-        <v>1013000000</v>
+        <v>281</v>
+      </c>
+      <c r="B251" s="2">
+        <v>3867240</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D251" s="3" t="s">
         <v>31</v>
@@ -11138,15 +11156,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="252" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="252" s="1" customFormat="1" spans="1:11">
       <c r="A252" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B252" s="4">
-        <v>1019000000</v>
+        <v>3882240</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D252" s="3" t="s">
         <v>31</v>
@@ -11173,15 +11191,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="253" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="253" s="1" customFormat="1" spans="1:11">
       <c r="A253" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="B253" s="4">
-        <v>1025000000</v>
+        <v>283</v>
+      </c>
+      <c r="B253" s="2">
+        <v>3897300</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D253" s="3" t="s">
         <v>31</v>
@@ -11208,15 +11226,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="254" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="254" s="1" customFormat="1" spans="1:11">
       <c r="A254" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B254" s="4">
-        <v>1943000000</v>
+        <v>4912420</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D254" s="3" t="s">
         <v>31</v>
@@ -11243,15 +11261,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="255" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="255" s="1" customFormat="1" spans="1:11">
       <c r="A255" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="B255" s="4">
-        <v>1955000000</v>
+        <v>285</v>
+      </c>
+      <c r="B255" s="2">
+        <v>4927600</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D255" s="3" t="s">
         <v>31</v>
@@ -11278,15 +11296,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="256" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="256" s="1" customFormat="1" spans="1:11">
       <c r="A256" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B256" s="4">
-        <v>1967000000</v>
+        <v>4942840</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D256" s="3" t="s">
         <v>31</v>
@@ -11313,15 +11331,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="257" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="257" s="1" customFormat="1" spans="1:11">
       <c r="A257" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B257" s="4">
-        <v>1979000000</v>
+        <v>287</v>
+      </c>
+      <c r="B257" s="2">
+        <v>4958140</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D257" s="3" t="s">
         <v>31</v>
@@ -11348,15 +11366,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="258" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="258" s="1" customFormat="1" spans="1:11">
       <c r="A258" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B258" s="4">
-        <v>1991000000</v>
+        <v>4973500</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D258" s="3" t="s">
         <v>31</v>
@@ -11383,15 +11401,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="259" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="259" s="1" customFormat="1" spans="1:11">
       <c r="A259" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="B259" s="4">
-        <v>2003000000</v>
+        <v>289</v>
+      </c>
+      <c r="B259" s="2">
+        <v>4988920</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D259" s="3" t="s">
         <v>31</v>
@@ -11418,15 +11436,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="260" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="260" s="1" customFormat="1" spans="1:11">
       <c r="A260" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B260" s="4">
-        <v>2015000000</v>
+        <v>5014400</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D260" s="3" t="s">
         <v>31</v>
@@ -11453,15 +11471,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="261" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="261" s="1" customFormat="1" spans="1:11">
       <c r="A261" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="B261" s="4">
-        <v>2027000000</v>
+        <v>291</v>
+      </c>
+      <c r="B261" s="2">
+        <v>5053940</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D261" s="3" t="s">
         <v>31</v>
@@ -11488,15 +11506,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="262" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="262" s="1" customFormat="1" spans="1:11">
       <c r="A262" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B262" s="4">
-        <v>2039000000</v>
+        <v>5099540</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D262" s="3" t="s">
         <v>31</v>
@@ -11523,15 +11541,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="263" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="263" s="1" customFormat="1" spans="1:11">
       <c r="A263" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="B263" s="4">
-        <v>2051000000</v>
+        <v>293</v>
+      </c>
+      <c r="B263" s="2">
+        <v>5151200</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D263" s="3" t="s">
         <v>31</v>
@@ -11558,15 +11576,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="264" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="264" s="1" customFormat="1" spans="1:11">
       <c r="A264" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B264" s="4">
-        <v>2058000000</v>
+        <v>5208920</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D264" s="3" t="s">
         <v>31</v>
@@ -11593,15 +11611,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="265" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="265" s="1" customFormat="1" spans="1:11">
       <c r="A265" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="B265" s="4">
-        <v>2070000000</v>
+        <v>295</v>
+      </c>
+      <c r="B265" s="2">
+        <v>5272700</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D265" s="3" t="s">
         <v>31</v>
@@ -11628,15 +11646,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="266" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="266" s="1" customFormat="1" spans="1:11">
       <c r="A266" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B266" s="4">
-        <v>2083000000</v>
+        <v>5342540</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D266" s="3" t="s">
         <v>31</v>
@@ -11663,15 +11681,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="267" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="267" s="1" customFormat="1" spans="1:11">
       <c r="A267" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="B267" s="4">
-        <v>2096000000</v>
+        <v>297</v>
+      </c>
+      <c r="B267" s="2">
+        <v>5418440</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D267" s="3" t="s">
         <v>31</v>
@@ -11698,15 +11716,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="268" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="268" s="1" customFormat="1" spans="1:11">
       <c r="A268" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B268" s="4">
-        <v>2108000000</v>
+        <v>5500400</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D268" s="3" t="s">
         <v>31</v>
@@ -11733,15 +11751,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="269" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="269" s="1" customFormat="1" spans="1:11">
       <c r="A269" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="B269" s="4">
-        <v>2121000000</v>
+        <v>299</v>
+      </c>
+      <c r="B269" s="2">
+        <v>5588420</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D269" s="3" t="s">
         <v>31</v>
@@ -11768,15 +11786,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="270" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="270" s="1" customFormat="1" spans="1:11">
       <c r="A270" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B270" s="4">
-        <v>2134000000</v>
+        <v>5682500</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D270" s="3" t="s">
         <v>31</v>
@@ -11803,15 +11821,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="271" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="271" s="1" customFormat="1" spans="1:11">
       <c r="A271" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="B271" s="4">
-        <v>2146000000</v>
+        <v>301</v>
+      </c>
+      <c r="B271" s="2">
+        <v>5782640</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D271" s="3" t="s">
         <v>31</v>
@@ -11838,15 +11856,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="272" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="272" s="1" customFormat="1" spans="1:11">
       <c r="A272" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B272" s="4">
-        <v>2159000000</v>
+        <v>5888840</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D272" s="3" t="s">
         <v>31</v>
@@ -11873,15 +11891,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="273" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="273" s="1" customFormat="1" spans="1:11">
       <c r="A273" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="B273" s="4">
-        <v>2172000000</v>
+        <v>303</v>
+      </c>
+      <c r="B273" s="2">
+        <v>6001100</v>
       </c>
       <c r="C273" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D273" s="3" t="s">
         <v>31</v>
@@ -11908,15 +11926,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="274" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="274" s="1" customFormat="1" spans="1:11">
       <c r="A274" s="1" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B274" s="4">
-        <v>2212000000</v>
+        <v>6119420</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D274" s="3" t="s">
         <v>31</v>
@@ -11943,15 +11961,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="275" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="275" s="1" customFormat="1" spans="1:11">
       <c r="A275" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="B275" s="4">
-        <v>2217000000</v>
+        <v>305</v>
+      </c>
+      <c r="B275" s="2">
+        <v>6243800</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D275" s="3" t="s">
         <v>31</v>
@@ -11978,15 +11996,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="276" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="276" s="1" customFormat="1" spans="1:11">
       <c r="A276" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B276" s="4">
-        <v>2221000000</v>
+        <v>6374240</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D276" s="3" t="s">
         <v>31</v>
@@ -12013,15 +12031,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="277" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="277" s="1" customFormat="1" spans="1:11">
       <c r="A277" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="B277" s="4">
-        <v>2225000000</v>
+        <v>307</v>
+      </c>
+      <c r="B277" s="2">
+        <v>6510740</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D277" s="3" t="s">
         <v>31</v>
@@ -12048,15 +12066,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="278" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="278" s="1" customFormat="1" spans="1:11">
       <c r="A278" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B278" s="4">
-        <v>2230000000</v>
+        <v>6653300</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D278" s="3" t="s">
         <v>31</v>
@@ -12083,15 +12101,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="279" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="279" s="1" customFormat="1" spans="1:11">
       <c r="A279" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="B279" s="4">
-        <v>2234000000</v>
+        <v>309</v>
+      </c>
+      <c r="B279" s="2">
+        <v>6801920</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D279" s="3" t="s">
         <v>31</v>
@@ -12118,15 +12136,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="280" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="280" s="1" customFormat="1" spans="1:11">
       <c r="A280" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B280" s="4">
-        <v>2239000000</v>
+        <v>6956600</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D280" s="3" t="s">
         <v>31</v>
@@ -12153,15 +12171,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="281" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="281" s="1" customFormat="1" spans="1:11">
       <c r="A281" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="B281" s="4">
-        <v>2243000000</v>
+        <v>311</v>
+      </c>
+      <c r="B281" s="2">
+        <v>7117340</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D281" s="3" t="s">
         <v>31</v>
@@ -12188,15 +12206,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="282" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="282" s="1" customFormat="1" spans="1:11">
       <c r="A282" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B282" s="4">
-        <v>2248000000</v>
+        <v>7284140</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D282" s="3" t="s">
         <v>31</v>
@@ -12223,15 +12241,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="283" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="283" s="1" customFormat="1" spans="1:11">
       <c r="A283" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="B283" s="4">
-        <v>2252000000</v>
+        <v>313</v>
+      </c>
+      <c r="B283" s="2">
+        <v>7457000</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D283" s="3" t="s">
         <v>31</v>
@@ -12258,15 +12276,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="284" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="284" s="1" customFormat="1" spans="1:11">
       <c r="A284" s="1" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B284" s="4">
-        <v>2328000000</v>
+        <v>7635920</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D284" s="3" t="s">
         <v>31</v>
@@ -12293,15 +12311,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="285" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="285" s="1" customFormat="1" spans="1:11">
       <c r="A285" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="B285" s="4">
-        <v>2333000000</v>
+        <v>315</v>
+      </c>
+      <c r="B285" s="2">
+        <v>7820900</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D285" s="3" t="s">
         <v>31</v>
@@ -12328,15 +12346,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="286" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="286" s="1" customFormat="1" spans="1:11">
       <c r="A286" s="1" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B286" s="4">
-        <v>2338000000</v>
+        <v>8011940</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D286" s="3" t="s">
         <v>31</v>
@@ -12363,15 +12381,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="287" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="287" s="1" customFormat="1" spans="1:11">
       <c r="A287" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="B287" s="4">
-        <v>2343000000</v>
+        <v>317</v>
+      </c>
+      <c r="B287" s="2">
+        <v>8209040</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D287" s="3" t="s">
         <v>31</v>
@@ -12398,15 +12416,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="288" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="288" s="1" customFormat="1" spans="1:11">
       <c r="A288" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B288" s="4">
-        <v>2347000000</v>
+        <v>8412200</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D288" s="3" t="s">
         <v>31</v>
@@ -12433,15 +12451,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="289" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="289" s="1" customFormat="1" spans="1:11">
       <c r="A289" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="B289" s="4">
-        <v>2352000000</v>
+        <v>319</v>
+      </c>
+      <c r="B289" s="2">
+        <v>8621420</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D289" s="3" t="s">
         <v>31</v>
@@ -12468,15 +12486,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="290" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="290" s="1" customFormat="1" spans="1:11">
       <c r="A290" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B290" s="4">
-        <v>2357000000</v>
+        <v>8836700</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D290" s="3" t="s">
         <v>31</v>
@@ -12503,15 +12521,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="291" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="291" s="1" customFormat="1" spans="1:11">
       <c r="A291" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B291" s="4">
-        <v>2361000000</v>
+        <v>321</v>
+      </c>
+      <c r="B291" s="2">
+        <v>9058040</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D291" s="3" t="s">
         <v>31</v>
@@ -12538,15 +12556,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="292" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="292" s="1" customFormat="1" spans="1:11">
       <c r="A292" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B292" s="4">
-        <v>2366000000</v>
+        <v>9285440</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D292" s="3" t="s">
         <v>31</v>
@@ -12573,15 +12591,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="293" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="293" s="1" customFormat="1" spans="1:11">
       <c r="A293" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="B293" s="4">
-        <v>2371000000</v>
+        <v>323</v>
+      </c>
+      <c r="B293" s="2">
+        <v>9518900</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D293" s="3" t="s">
         <v>31</v>
@@ -12608,15 +12626,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="294" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="294" s="1" customFormat="1" spans="1:11">
       <c r="A294" s="1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B294" s="4">
-        <v>4745000000</v>
+        <v>9758420</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D294" s="3" t="s">
         <v>31</v>
@@ -12643,15 +12661,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="295" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="295" s="1" customFormat="1" spans="1:11">
       <c r="A295" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="B295" s="4">
-        <v>4755000000</v>
+        <v>325</v>
+      </c>
+      <c r="B295" s="2">
+        <v>13004000</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D295" s="3" t="s">
         <v>31</v>
@@ -12678,15 +12696,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="296" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="296" s="1" customFormat="1" spans="1:11">
       <c r="A296" s="1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B296" s="4">
-        <v>4764000000</v>
+        <v>13255640</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D296" s="3" t="s">
         <v>31</v>
@@ -12713,15 +12731,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="297" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="297" s="1" customFormat="1" spans="1:11">
       <c r="A297" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="B297" s="4">
-        <v>4774000000</v>
+        <v>327</v>
+      </c>
+      <c r="B297" s="2">
+        <v>13513340</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D297" s="3" t="s">
         <v>31</v>
@@ -12748,15 +12766,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="298" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="298" s="1" customFormat="1" spans="1:11">
       <c r="A298" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B298" s="4">
-        <v>4783000000</v>
+        <v>13777100</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D298" s="3" t="s">
         <v>31</v>
@@ -12783,15 +12801,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="299" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="299" s="1" customFormat="1" spans="1:11">
       <c r="A299" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="B299" s="4">
-        <v>4793000000</v>
+        <v>329</v>
+      </c>
+      <c r="B299" s="2">
+        <v>14046920</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D299" s="3" t="s">
         <v>31</v>
@@ -12818,15 +12836,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="300" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="300" s="1" customFormat="1" spans="1:11">
       <c r="A300" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B300" s="4">
-        <v>4803000000</v>
+        <v>14322800</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D300" s="3" t="s">
         <v>31</v>
@@ -12853,15 +12871,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="301" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="301" s="1" customFormat="1" spans="1:11">
       <c r="A301" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B301" s="4">
-        <v>4812000000</v>
+        <v>331</v>
+      </c>
+      <c r="B301" s="2">
+        <v>14604740</v>
       </c>
       <c r="C301" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D301" s="3" t="s">
         <v>31</v>
@@ -12888,15 +12906,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="302" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="302" s="1" customFormat="1" spans="1:11">
       <c r="A302" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B302" s="4">
-        <v>4822000000</v>
+        <v>14892740</v>
       </c>
       <c r="C302" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D302" s="3" t="s">
         <v>31</v>
@@ -12923,15 +12941,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="303" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="303" s="1" customFormat="1" spans="1:11">
       <c r="A303" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="B303" s="4">
-        <v>4831000000</v>
+        <v>333</v>
+      </c>
+      <c r="B303" s="2">
+        <v>15186800</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D303" s="3" t="s">
         <v>31</v>
@@ -12958,15 +12976,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="304" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="304" s="1" customFormat="1" spans="1:11">
       <c r="A304" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B304" s="4">
-        <v>4971000000</v>
+        <v>15486920</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D304" s="3" t="s">
         <v>31</v>
@@ -12993,15 +13011,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="305" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="305" s="1" customFormat="1" spans="1:11">
       <c r="A305" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="B305" s="4">
-        <v>4981000000</v>
+        <v>335</v>
+      </c>
+      <c r="B305" s="2">
+        <v>15793100</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D305" s="3" t="s">
         <v>31</v>
@@ -13028,15 +13046,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="306" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="306" s="1" customFormat="1" spans="1:11">
       <c r="A306" s="1" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B306" s="4">
-        <v>4991000000</v>
+        <v>18105340</v>
       </c>
       <c r="C306" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D306" s="3" t="s">
         <v>31</v>
@@ -13063,15 +13081,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="307" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="307" s="1" customFormat="1" spans="1:11">
       <c r="A307" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B307" s="4">
-        <v>5001000000</v>
+        <v>337</v>
+      </c>
+      <c r="B307" s="2">
+        <v>18423640</v>
       </c>
       <c r="C307" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D307" s="3" t="s">
         <v>31</v>
@@ -13098,15 +13116,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="308" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="308" s="1" customFormat="1" spans="1:11">
       <c r="A308" s="1" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B308" s="4">
-        <v>5011000000</v>
+        <v>18748000</v>
       </c>
       <c r="C308" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D308" s="3" t="s">
         <v>31</v>
@@ -13133,15 +13151,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="309" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="309" s="1" customFormat="1" spans="1:11">
       <c r="A309" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="B309" s="4">
-        <v>5021000000</v>
+        <v>339</v>
+      </c>
+      <c r="B309" s="2">
+        <v>19078420</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D309" s="3" t="s">
         <v>31</v>
@@ -13168,15 +13186,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="310" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="310" s="1" customFormat="1" spans="1:11">
       <c r="A310" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B310" s="4">
-        <v>5031000000</v>
+        <v>19414900</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D310" s="3" t="s">
         <v>31</v>
@@ -13203,15 +13221,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="311" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="311" s="1" customFormat="1" spans="1:11">
       <c r="A311" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="B311" s="4">
-        <v>5041000000</v>
+        <v>341</v>
+      </c>
+      <c r="B311" s="2">
+        <v>19757440</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D311" s="3" t="s">
         <v>31</v>
@@ -13238,15 +13256,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="312" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="312" s="1" customFormat="1" spans="1:11">
       <c r="A312" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B312" s="4">
-        <v>5051000000</v>
+        <v>20106040</v>
       </c>
       <c r="C312" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D312" s="3" t="s">
         <v>31</v>
@@ -13273,15 +13291,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="313" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="313" s="1" customFormat="1" spans="1:11">
       <c r="A313" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="B313" s="4">
-        <v>5061000000</v>
+        <v>343</v>
+      </c>
+      <c r="B313" s="2">
+        <v>20460700</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D313" s="3" t="s">
         <v>31</v>
@@ -13308,15 +13326,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="314" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="314" s="1" customFormat="1" spans="1:11">
       <c r="A314" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B314" s="4">
-        <v>5197000000</v>
+        <v>20821420</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D314" s="3" t="s">
         <v>31</v>
@@ -13343,15 +13361,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="315" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="315" s="1" customFormat="1" spans="1:11">
       <c r="A315" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="B315" s="4">
-        <v>5208000000</v>
+        <v>345</v>
+      </c>
+      <c r="B315" s="2">
+        <v>22188200</v>
       </c>
       <c r="C315" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D315" s="3" t="s">
         <v>31</v>
@@ -13378,15 +13396,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="316" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="316" s="1" customFormat="1" spans="1:11">
       <c r="A316" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B316" s="4">
-        <v>5218000000</v>
+        <v>22561040</v>
       </c>
       <c r="C316" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D316" s="3" t="s">
         <v>31</v>
@@ -13413,15 +13431,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="317" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="317" s="1" customFormat="1" spans="1:11">
       <c r="A317" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="B317" s="4">
-        <v>5229000000</v>
+        <v>347</v>
+      </c>
+      <c r="B317" s="2">
+        <v>23939940</v>
       </c>
       <c r="C317" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D317" s="3" t="s">
         <v>31</v>
@@ -13448,15 +13466,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="318" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="318" s="1" customFormat="1" spans="1:11">
       <c r="A318" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B318" s="4">
-        <v>5239000000</v>
+        <v>24324900</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D318" s="3" t="s">
         <v>31</v>
@@ -13483,15 +13501,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="319" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="319" s="1" customFormat="1" spans="1:11">
       <c r="A319" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="B319" s="4">
-        <v>5249000000</v>
+        <v>349</v>
+      </c>
+      <c r="B319" s="2">
+        <v>25715920</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D319" s="3" t="s">
         <v>31</v>
@@ -13518,15 +13536,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="320" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="320" s="1" customFormat="1" spans="1:11">
       <c r="A320" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B320" s="4">
-        <v>5260000000</v>
+        <v>26113000</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D320" s="3" t="s">
         <v>31</v>
@@ -13553,15 +13571,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="321" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="321" s="1" customFormat="1" spans="1:11">
       <c r="A321" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="B321" s="4">
-        <v>5270000000</v>
+        <v>351</v>
+      </c>
+      <c r="B321" s="2">
+        <v>27516140</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D321" s="3" t="s">
         <v>31</v>
@@ -13588,15 +13606,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="322" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="322" s="1" customFormat="1" spans="1:11">
       <c r="A322" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B322" s="4">
-        <v>5281000000</v>
+        <v>28925340</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D322" s="3" t="s">
         <v>31</v>
@@ -13623,15 +13641,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="323" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="323" s="1" customFormat="1" spans="1:11">
       <c r="A323" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="B323" s="4">
-        <v>5291000000</v>
+        <v>353</v>
+      </c>
+      <c r="B323" s="2">
+        <v>29340600</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D323" s="3" t="s">
         <v>31</v>
@@ -13658,15 +13676,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="324" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="324" s="1" customFormat="1" spans="1:11">
       <c r="A324" s="1" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B324" s="4">
-        <v>5420000000</v>
+        <v>30761920</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D324" s="3" t="s">
         <v>31</v>
@@ -13693,15 +13711,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="325" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="325" s="1" customFormat="1" spans="1:11">
       <c r="A325" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="B325" s="4">
-        <v>5430000000</v>
+        <v>355</v>
+      </c>
+      <c r="B325" s="2">
+        <v>31189300</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D325" s="3" t="s">
         <v>31</v>
@@ -13728,15 +13746,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="326" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="326" s="1" customFormat="1" spans="1:11">
       <c r="A326" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B326" s="4">
-        <v>5440000000</v>
+        <v>32622740</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D326" s="3" t="s">
         <v>31</v>
@@ -13763,15 +13781,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="327" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="327" s="1" customFormat="1" spans="1:11">
       <c r="A327" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="B327" s="4">
-        <v>5460000000</v>
+        <v>357</v>
+      </c>
+      <c r="B327" s="2">
+        <v>33062240</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D327" s="3" t="s">
         <v>31</v>
@@ -13798,15 +13816,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="328" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="328" s="1" customFormat="1" spans="1:11">
       <c r="A328" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B328" s="4">
-        <v>5470000000</v>
+        <v>34507800</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D328" s="3" t="s">
         <v>31</v>
@@ -13833,15 +13851,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="329" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="329" s="1" customFormat="1" spans="1:11">
       <c r="A329" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="B329" s="4">
-        <v>5480000000</v>
+        <v>359</v>
+      </c>
+      <c r="B329" s="2">
+        <v>35959420</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D329" s="3" t="s">
         <v>31</v>
@@ -13868,15 +13886,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="330" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="330" s="1" customFormat="1" spans="1:11">
       <c r="A330" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B330" s="4">
-        <v>5490000000</v>
+        <v>36417100</v>
       </c>
       <c r="C330" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D330" s="3" t="s">
         <v>31</v>
@@ -13903,15 +13921,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="331" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="331" s="1" customFormat="1" spans="1:11">
       <c r="A331" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="B331" s="4">
-        <v>5500000000</v>
+        <v>361</v>
+      </c>
+      <c r="B331" s="2">
+        <v>37880840</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D331" s="3" t="s">
         <v>31</v>
@@ -13938,15 +13956,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="332" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="332" s="1" customFormat="1" spans="1:11">
       <c r="A332" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B332" s="4">
-        <v>5510000000</v>
+        <v>38350640</v>
       </c>
       <c r="C332" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D332" s="3" t="s">
         <v>31</v>
@@ -13973,15 +13991,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="333" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="333" s="1" customFormat="1" spans="1:11">
       <c r="A333" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="B333" s="4">
-        <v>5520000000</v>
+        <v>363</v>
+      </c>
+      <c r="B333" s="2">
+        <v>39826500</v>
       </c>
       <c r="C333" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D333" s="3" t="s">
         <v>31</v>
@@ -14008,15 +14026,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="334" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="334" s="1" customFormat="1" spans="1:11">
       <c r="A334" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B334" s="4">
-        <v>11790000000</v>
+        <v>40308420</v>
       </c>
       <c r="C334" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D334" s="3" t="s">
         <v>31</v>
@@ -14043,15 +14061,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="335" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="335" s="1" customFormat="1" spans="1:11">
       <c r="A335" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="B335" s="4">
-        <v>11810000000</v>
+        <v>365</v>
+      </c>
+      <c r="B335" s="2">
+        <v>41796400</v>
       </c>
       <c r="C335" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D335" s="3" t="s">
         <v>31</v>
@@ -14078,15 +14096,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="336" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="336" s="1" customFormat="1" spans="1:11">
       <c r="A336" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B336" s="4">
-        <v>11840000000</v>
+        <v>42290440</v>
       </c>
       <c r="C336" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D336" s="3" t="s">
         <v>31</v>
@@ -14113,15 +14131,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="337" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="337" s="1" customFormat="1" spans="1:11">
       <c r="A337" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="B337" s="4">
-        <v>11860000000</v>
+        <v>367</v>
+      </c>
+      <c r="B337" s="2">
+        <v>43790540</v>
       </c>
       <c r="C337" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D337" s="3" t="s">
         <v>31</v>
@@ -14148,15 +14166,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="338" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="338" s="1" customFormat="1" spans="1:11">
       <c r="A338" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B338" s="4">
-        <v>11890000000</v>
+        <v>44296700</v>
       </c>
       <c r="C338" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D338" s="3" t="s">
         <v>31</v>
@@ -14183,15 +14201,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="339" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="339" s="1" customFormat="1" spans="1:11">
       <c r="A339" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="B339" s="4">
-        <v>11910000000</v>
+        <v>369</v>
+      </c>
+      <c r="B339" s="2">
+        <v>45808920</v>
       </c>
       <c r="C339" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D339" s="3" t="s">
         <v>31</v>
@@ -14218,15 +14236,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="340" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="340" s="1" customFormat="1" spans="1:11">
       <c r="A340" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B340" s="4">
-        <v>11930000000</v>
+        <v>46327200</v>
       </c>
       <c r="C340" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D340" s="3" t="s">
         <v>31</v>
@@ -14253,15 +14271,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="341" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="341" s="1" customFormat="1" spans="1:11">
       <c r="A341" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="B341" s="4">
-        <v>11960000000</v>
+        <v>371</v>
+      </c>
+      <c r="B341" s="2">
+        <v>47851540</v>
       </c>
       <c r="C341" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D341" s="3" t="s">
         <v>31</v>
@@ -14288,15 +14306,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="342" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="342" s="1" customFormat="1" spans="1:11">
       <c r="A342" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B342" s="4">
-        <v>11980000000</v>
+        <v>48381940</v>
       </c>
       <c r="C342" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D342" s="3" t="s">
         <v>31</v>
@@ -14323,15 +14341,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="343" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="343" s="1" customFormat="1" spans="1:11">
       <c r="A343" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="B343" s="4">
-        <v>12000000000</v>
+        <v>373</v>
+      </c>
+      <c r="B343" s="2">
+        <v>49918400</v>
       </c>
       <c r="C343" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D343" s="3" t="s">
         <v>31</v>
@@ -14358,15 +14376,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="344" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="344" s="1" customFormat="1" spans="1:11">
       <c r="A344" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B344" s="4">
-        <v>12260000000</v>
+        <v>50460920</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D344" s="3" t="s">
         <v>31</v>
@@ -14393,15 +14411,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="345" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="345" s="1" customFormat="1" spans="1:11">
       <c r="A345" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="B345" s="4">
-        <v>12290000000</v>
+        <v>375</v>
+      </c>
+      <c r="B345" s="2">
+        <v>74009500</v>
       </c>
       <c r="C345" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D345" s="3" t="s">
         <v>31</v>
@@ -14428,15 +14446,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="346" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="346" s="1" customFormat="1" spans="1:11">
       <c r="A346" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B346" s="4">
-        <v>12310000000</v>
+        <v>75564140</v>
       </c>
       <c r="C346" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D346" s="3" t="s">
         <v>31</v>
@@ -14463,15 +14481,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="347" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="347" s="1" customFormat="1" spans="1:11">
       <c r="A347" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="B347" s="4">
-        <v>12340000000</v>
+        <v>377</v>
+      </c>
+      <c r="B347" s="2">
+        <v>76124840</v>
       </c>
       <c r="C347" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D347" s="3" t="s">
         <v>31</v>
@@ -14498,15 +14516,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="348" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="348" s="1" customFormat="1" spans="1:11">
       <c r="A348" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B348" s="4">
-        <v>12360000000</v>
+        <v>76691600</v>
       </c>
       <c r="C348" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D348" s="3" t="s">
         <v>31</v>
@@ -14533,15 +14551,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="349" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="349" s="1" customFormat="1" spans="1:11">
       <c r="A349" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="B349" s="4">
-        <v>12390000000</v>
+        <v>379</v>
+      </c>
+      <c r="B349" s="2">
+        <v>77264420</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D349" s="3" t="s">
         <v>31</v>
@@ -14568,15 +14586,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="350" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="350" s="1" customFormat="1" spans="1:11">
       <c r="A350" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B350" s="4">
-        <v>12410000000</v>
+        <v>78843300</v>
       </c>
       <c r="C350" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D350" s="3" t="s">
         <v>31</v>
@@ -14603,15 +14621,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="351" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="351" s="1" customFormat="1" spans="1:11">
       <c r="A351" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="B351" s="4">
-        <v>12440000000</v>
+        <v>381</v>
+      </c>
+      <c r="B351" s="2">
+        <v>78428240</v>
       </c>
       <c r="C351" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D351" s="3" t="s">
         <v>31</v>
@@ -14638,15 +14656,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="352" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="352" s="1" customFormat="1" spans="1:11">
       <c r="A352" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B352" s="4">
-        <v>12460000000</v>
+        <v>80019240</v>
       </c>
       <c r="C352" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D352" s="3" t="s">
         <v>31</v>
@@ -14673,15 +14691,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="353" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="353" s="1" customFormat="1" spans="1:11">
       <c r="A353" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="B353" s="4">
-        <v>12480000000</v>
+        <v>383</v>
+      </c>
+      <c r="B353" s="2">
+        <v>81616300</v>
       </c>
       <c r="C353" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D353" s="3" t="s">
         <v>31</v>
@@ -14708,15 +14726,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="354" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="354" s="1" customFormat="1" spans="1:11">
       <c r="A354" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B354" s="4">
-        <v>12730000000</v>
+        <v>82219420</v>
       </c>
       <c r="C354" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D354" s="3" t="s">
         <v>31</v>
@@ -14743,15 +14761,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="355" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="355" s="1" customFormat="1" spans="1:11">
       <c r="A355" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="B355" s="4">
-        <v>12760000000</v>
+        <v>385</v>
+      </c>
+      <c r="B355" s="2">
+        <v>84828600</v>
       </c>
       <c r="C355" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D355" s="3" t="s">
         <v>31</v>
@@ -14778,15 +14796,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="356" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="356" s="1" customFormat="1" spans="1:11">
       <c r="A356" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B356" s="4">
-        <v>12790000000</v>
+        <v>84443840</v>
       </c>
       <c r="C356" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D356" s="3" t="s">
         <v>31</v>
@@ -14813,15 +14831,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="357" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="357" s="1" customFormat="1" spans="1:11">
       <c r="A357" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="B357" s="4">
-        <v>12810000000</v>
+        <v>387</v>
+      </c>
+      <c r="B357" s="2">
+        <v>86065140</v>
       </c>
       <c r="C357" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D357" s="3" t="s">
         <v>31</v>
@@ -14848,15 +14866,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="358" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="358" s="1" customFormat="1" spans="1:11">
       <c r="A358" s="1" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B358" s="4">
-        <v>12840000000</v>
+        <v>88692500</v>
       </c>
       <c r="C358" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D358" s="3" t="s">
         <v>31</v>
@@ -14883,15 +14901,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="359" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="359" s="1" customFormat="1" spans="1:11">
       <c r="A359" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="B359" s="4">
-        <v>12860000000</v>
+        <v>389</v>
+      </c>
+      <c r="B359" s="2">
+        <v>90325920</v>
       </c>
       <c r="C359" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D359" s="3" t="s">
         <v>31</v>
@@ -14918,15 +14936,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="360" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="360" s="1" customFormat="1" spans="1:11">
       <c r="A360" s="1" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B360" s="4">
-        <v>12890000000</v>
+        <v>90965400</v>
       </c>
       <c r="C360" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D360" s="3" t="s">
         <v>31</v>
@@ -14953,15 +14971,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="361" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="361" s="1" customFormat="1" spans="1:11">
       <c r="A361" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="B361" s="4">
-        <v>12910000000</v>
+        <v>391</v>
+      </c>
+      <c r="B361" s="2">
+        <v>91610940</v>
       </c>
       <c r="C361" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D361" s="3" t="s">
         <v>31</v>
@@ -14988,15 +15006,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="362" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="362" s="1" customFormat="1" spans="1:11">
       <c r="A362" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B362" s="4">
-        <v>12940000000</v>
+        <v>92262540</v>
       </c>
       <c r="C362" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D362" s="3" t="s">
         <v>31</v>
@@ -15023,15 +15041,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="363" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="363" s="1" customFormat="1" spans="1:11">
       <c r="A363" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="B363" s="4">
-        <v>12970000000</v>
+        <v>393</v>
+      </c>
+      <c r="B363" s="2">
+        <v>93920200</v>
       </c>
       <c r="C363" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D363" s="3" t="s">
         <v>31</v>
@@ -15058,15 +15076,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="364" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="364" s="1" customFormat="1" spans="1:11">
       <c r="A364" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B364" s="4">
-        <v>13210000000</v>
+        <v>98583920</v>
       </c>
       <c r="C364" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D364" s="3" t="s">
         <v>31</v>
@@ -15093,15 +15111,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="365" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="365" s="1" customFormat="1" spans="1:11">
       <c r="A365" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="B365" s="4">
-        <v>13230000000</v>
+        <v>395</v>
+      </c>
+      <c r="B365" s="2">
+        <v>99253700</v>
       </c>
       <c r="C365" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D365" s="3" t="s">
         <v>31</v>
@@ -15128,15 +15146,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="366" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="366" s="1" customFormat="1" spans="1:11">
       <c r="A366" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B366" s="4">
-        <v>13260000000</v>
+        <v>100929540</v>
       </c>
       <c r="C366" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D366" s="3" t="s">
         <v>31</v>
@@ -15163,15 +15181,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="367" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="367" s="1" customFormat="1" spans="1:11">
       <c r="A367" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="B367" s="4">
-        <v>13290000000</v>
+        <v>397</v>
+      </c>
+      <c r="B367" s="2">
+        <v>1010611440</v>
       </c>
       <c r="C367" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D367" s="3" t="s">
         <v>31</v>
@@ -15198,15 +15216,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="368" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="368" s="1" customFormat="1" spans="1:11">
       <c r="A368" s="1" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B368" s="4">
-        <v>13310000000</v>
+        <v>1021299400</v>
       </c>
       <c r="C368" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D368" s="3" t="s">
         <v>31</v>
@@ -15233,15 +15251,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="369" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="369" s="1" customFormat="1" spans="1:11">
       <c r="A369" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="B369" s="4">
-        <v>13340000000</v>
+        <v>399</v>
+      </c>
+      <c r="B369" s="2">
+        <v>1031993420</v>
       </c>
       <c r="C369" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D369" s="3" t="s">
         <v>31</v>
@@ -15268,15 +15286,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="370" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="370" s="1" customFormat="1" spans="1:11">
       <c r="A370" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B370" s="4">
-        <v>13370000000</v>
+        <v>1142693500</v>
       </c>
       <c r="C370" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D370" s="3" t="s">
         <v>31</v>
@@ -15303,15 +15321,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="371" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="371" s="1" customFormat="1" spans="1:11">
       <c r="A371" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="B371" s="4">
-        <v>13390000000</v>
+        <v>401</v>
+      </c>
+      <c r="B371" s="2">
+        <v>1153399640</v>
       </c>
       <c r="C371" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D371" s="3" t="s">
         <v>31</v>
@@ -15338,15 +15356,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="372" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="372" s="1" customFormat="1" spans="1:11">
       <c r="A372" s="1" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B372" s="4">
-        <v>13420000000</v>
+        <v>1164111840</v>
       </c>
       <c r="C372" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D372" s="3" t="s">
         <v>31</v>
@@ -15373,15 +15391,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="373" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="373" s="1" customFormat="1" spans="1:11">
       <c r="A373" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="B373" s="4">
-        <v>13450000000</v>
+        <v>403</v>
+      </c>
+      <c r="B373" s="2">
+        <v>1174830100</v>
       </c>
       <c r="C373" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D373" s="3" t="s">
         <v>31</v>
@@ -15408,15 +15426,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="374" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="374" s="1" customFormat="1" spans="1:11">
       <c r="A374" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B374" s="4">
-        <v>26930000000</v>
+        <v>1185554420</v>
       </c>
       <c r="C374" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D374" s="3" t="s">
         <v>31</v>
@@ -15443,15 +15461,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="375" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="375" s="1" customFormat="1" spans="1:11">
       <c r="A375" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="B375" s="4">
-        <v>26990000000</v>
+        <v>405</v>
+      </c>
+      <c r="B375" s="2">
+        <v>1196284800</v>
       </c>
       <c r="C375" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D375" s="3" t="s">
         <v>31</v>
@@ -15478,15 +15496,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="376" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="376" s="1" customFormat="1" spans="1:11">
       <c r="A376" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B376" s="4">
-        <v>27040000000</v>
+        <v>1207021240</v>
       </c>
       <c r="C376" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D376" s="3" t="s">
         <v>31</v>
@@ -15513,15 +15531,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="377" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="377" s="1" customFormat="1" spans="1:11">
       <c r="A377" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="B377" s="4">
-        <v>27100000000</v>
+        <v>407</v>
+      </c>
+      <c r="B377" s="2">
+        <v>1287763740</v>
       </c>
       <c r="C377" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D377" s="3" t="s">
         <v>31</v>
@@ -15548,15 +15566,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="378" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="378" s="1" customFormat="1" spans="1:11">
       <c r="A378" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B378" s="4">
-        <v>27150000000</v>
+        <v>1288512300</v>
       </c>
       <c r="C378" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D378" s="3" t="s">
         <v>31</v>
@@ -15583,15 +15601,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="379" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="379" s="1" customFormat="1" spans="1:11">
       <c r="A379" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="B379" s="4">
-        <v>27200000000</v>
+        <v>409</v>
+      </c>
+      <c r="B379" s="2">
+        <v>1289266920</v>
       </c>
       <c r="C379" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D379" s="3" t="s">
         <v>31</v>
@@ -15618,15 +15636,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="380" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="380" s="1" customFormat="1" spans="1:11">
       <c r="A380" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B380" s="4">
-        <v>27260000000</v>
+        <v>1400027600</v>
       </c>
       <c r="C380" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D380" s="3" t="s">
         <v>31</v>
@@ -15653,15 +15671,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="381" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="381" s="1" customFormat="1" spans="1:11">
       <c r="A381" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="B381" s="4">
-        <v>27310000000</v>
+        <v>411</v>
+      </c>
+      <c r="B381" s="2">
+        <v>1500794340</v>
       </c>
       <c r="C381" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D381" s="3" t="s">
         <v>31</v>
@@ -15688,15 +15706,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="382" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="382" s="1" customFormat="1" spans="1:11">
       <c r="A382" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B382" s="4">
-        <v>27370000000</v>
+        <v>1601567140</v>
       </c>
       <c r="C382" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D382" s="3" t="s">
         <v>31</v>
@@ -15723,15 +15741,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="383" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="383" s="1" customFormat="1" spans="1:11">
       <c r="A383" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="B383" s="4">
-        <v>27420000000</v>
+        <v>413</v>
+      </c>
+      <c r="B383" s="2">
+        <v>1702346000</v>
       </c>
       <c r="C383" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D383" s="3" t="s">
         <v>31</v>
@@ -15758,15 +15776,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="384" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="384" s="1" customFormat="1" spans="1:11">
       <c r="A384" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B384" s="4">
-        <v>139300000000</v>
+        <v>1803130920</v>
       </c>
       <c r="C384" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D384" s="3" t="s">
         <v>31</v>
@@ -15793,15 +15811,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="385" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="385" s="1" customFormat="1" spans="1:11">
       <c r="A385" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="B385" s="4">
-        <v>139600000000</v>
+        <v>415</v>
+      </c>
+      <c r="B385" s="2">
+        <v>1853921900</v>
       </c>
       <c r="C385" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D385" s="3" t="s">
         <v>31</v>
@@ -15828,15 +15846,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="386" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="386" s="1" customFormat="1" spans="1:11">
       <c r="A386" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B386" s="4">
-        <v>139850000000</v>
+        <v>1854718940</v>
       </c>
       <c r="C386" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D386" s="3" t="s">
         <v>31</v>
@@ -15863,15 +15881,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="387" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="387" s="1" customFormat="1" spans="1:11">
       <c r="A387" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="B387" s="4">
-        <v>140150000000</v>
+        <v>417</v>
+      </c>
+      <c r="B387" s="2">
+        <v>1855522040</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D387" s="3" t="s">
         <v>31</v>
@@ -15898,15 +15916,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="388" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="388" s="1" customFormat="1" spans="1:11">
       <c r="A388" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B388" s="4">
-        <v>140450000000</v>
+        <v>1856331200</v>
       </c>
       <c r="C388" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D388" s="3" t="s">
         <v>31</v>
@@ -15933,15 +15951,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="389" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="389" s="1" customFormat="1" spans="1:11">
       <c r="A389" s="1" t="s">
-        <v>418</v>
-      </c>
-      <c r="B389" s="4">
-        <v>140700000000</v>
+        <v>419</v>
+      </c>
+      <c r="B389" s="2">
+        <v>1857146420</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D389" s="3" t="s">
         <v>31</v>
@@ -15968,15 +15986,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="390" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="390" s="1" customFormat="1" spans="1:11">
       <c r="A390" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B390" s="4">
-        <v>141000000000</v>
+        <v>1857967700</v>
       </c>
       <c r="C390" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D390" s="3" t="s">
         <v>31</v>
@@ -16003,15 +16021,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="391" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="391" s="1" customFormat="1" spans="1:11">
       <c r="A391" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="B391" s="4">
-        <v>141300000000</v>
+        <v>421</v>
+      </c>
+      <c r="B391" s="2">
+        <v>1858795040</v>
       </c>
       <c r="C391" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D391" s="3" t="s">
         <v>31</v>
@@ -16038,15 +16056,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="392" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="392" s="1" customFormat="1" spans="1:11">
       <c r="A392" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B392" s="4">
-        <v>141550000000</v>
+        <v>1859628440</v>
       </c>
       <c r="C392" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D392" s="3" t="s">
         <v>31</v>
@@ -16073,15 +16091,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="393" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="393" s="1" customFormat="1" spans="1:11">
       <c r="A393" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="B393" s="4">
-        <v>141850000000</v>
+        <v>423</v>
+      </c>
+      <c r="B393" s="2">
+        <v>1960467900</v>
       </c>
       <c r="C393" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D393" s="3" t="s">
         <v>31</v>
@@ -16108,15 +16126,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="394" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="394" s="1" customFormat="1" spans="1:11">
       <c r="A394" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B394" s="4">
-        <v>143950000000</v>
+        <v>1961313420</v>
       </c>
       <c r="C394" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D394" s="3" t="s">
         <v>31</v>
@@ -16143,15 +16161,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="395" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="395" s="1" customFormat="1" spans="1:11">
       <c r="A395" s="1" t="s">
-        <v>424</v>
-      </c>
-      <c r="B395" s="4">
-        <v>144250000000</v>
+        <v>425</v>
+      </c>
+      <c r="B395" s="2">
+        <v>1962165000</v>
       </c>
       <c r="C395" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D395" s="3" t="s">
         <v>31</v>
@@ -16178,15 +16196,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="396" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="396" s="1" customFormat="1" spans="1:11">
       <c r="A396" s="1" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B396" s="4">
-        <v>144550000000</v>
+        <v>1963022640</v>
       </c>
       <c r="C396" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D396" s="3" t="s">
         <v>31</v>
@@ -16213,15 +16231,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="397" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="397" s="1" customFormat="1" spans="1:11">
       <c r="A397" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="B397" s="4">
-        <v>144800000000</v>
+        <v>427</v>
+      </c>
+      <c r="B397" s="2">
+        <v>1963886340</v>
       </c>
       <c r="C397" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D397" s="3" t="s">
         <v>31</v>
@@ -16248,15 +16266,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="398" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="398" s="1" customFormat="1" spans="1:11">
       <c r="A398" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B398" s="4">
-        <v>145100000000</v>
+        <v>1964756100</v>
       </c>
       <c r="C398" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D398" s="3" t="s">
         <v>31</v>
@@ -16283,15 +16301,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="399" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="399" s="1" customFormat="1" spans="1:11">
       <c r="A399" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="B399" s="4">
-        <v>145400000000</v>
+        <v>429</v>
+      </c>
+      <c r="B399" s="2">
+        <v>1965631920</v>
       </c>
       <c r="C399" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D399" s="3" t="s">
         <v>31</v>
@@ -16318,15 +16336,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="400" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="400" s="1" customFormat="1" spans="1:11">
       <c r="A400" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B400" s="4">
-        <v>145700000000</v>
+        <v>1966513800</v>
       </c>
       <c r="C400" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D400" s="3" t="s">
         <v>31</v>
@@ -16353,15 +16371,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="401" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="401" s="1" customFormat="1" spans="1:11">
       <c r="A401" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="B401" s="4">
-        <v>146000000000</v>
+        <v>431</v>
+      </c>
+      <c r="B401" s="2">
+        <v>1967401740</v>
       </c>
       <c r="C401" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D401" s="3" t="s">
         <v>31</v>
@@ -16388,15 +16406,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="402" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="402" s="1" customFormat="1" spans="1:11">
       <c r="A402" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B402" s="4">
-        <v>146250000000</v>
+        <v>2068295740</v>
       </c>
       <c r="C402" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D402" s="3" t="s">
         <v>31</v>
@@ -16423,15 +16441,15 @@
         <v>32</v>
       </c>
     </row>
-    <row r="403" s="1" customFormat="1" ht="14.25" spans="1:11">
+    <row r="403" s="1" customFormat="1" spans="1:11">
       <c r="A403" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="B403" s="4">
-        <v>146550000000</v>
+        <v>433</v>
+      </c>
+      <c r="B403" s="2">
+        <v>2169195800</v>
       </c>
       <c r="C403" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D403" s="3" t="s">
         <v>31</v>
@@ -16460,11 +16478,11 @@
     </row>
     <row r="404" s="1" customFormat="1" ht="16.5" spans="1:11">
       <c r="A404" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B404" s="5"/>
       <c r="C404" s="1" t="s">
-        <v>30</v>
+        <v>255</v>
       </c>
       <c r="D404" s="3" t="s">
         <v>31</v>

--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_level.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/In/cfg_level.xlsx
@@ -3,8 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\In\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -7167,8 +7172,8 @@
       <c r="A104" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B104" s="4">
-        <v>314920</v>
+      <c r="B104" s="2">
+        <v>2100000</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>30</v>
@@ -7203,7 +7208,7 @@
         <v>134</v>
       </c>
       <c r="B105" s="2">
-        <v>321100</v>
+        <v>2100000</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>30</v>
@@ -7237,8 +7242,8 @@
       <c r="A106" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B106" s="4">
-        <v>327340</v>
+      <c r="B106" s="2">
+        <v>2100000</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>30</v>
@@ -7273,7 +7278,7 @@
         <v>136</v>
       </c>
       <c r="B107" s="2">
-        <v>333640</v>
+        <v>2100000</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>30</v>
@@ -7307,8 +7312,8 @@
       <c r="A108" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B108" s="4">
-        <v>340000</v>
+      <c r="B108" s="2">
+        <v>2100000</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>30</v>
@@ -7343,7 +7348,7 @@
         <v>138</v>
       </c>
       <c r="B109" s="2">
-        <v>346420</v>
+        <v>2100000</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>30</v>
@@ -7377,8 +7382,8 @@
       <c r="A110" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B110" s="4">
-        <v>352900</v>
+      <c r="B110" s="2">
+        <v>2100000</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>30</v>
@@ -7413,7 +7418,7 @@
         <v>140</v>
       </c>
       <c r="B111" s="2">
-        <v>359440</v>
+        <v>2100000</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>30</v>
@@ -7447,8 +7452,8 @@
       <c r="A112" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B112" s="4">
-        <v>366040</v>
+      <c r="B112" s="2">
+        <v>2100000</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>30</v>
@@ -7483,7 +7488,7 @@
         <v>142</v>
       </c>
       <c r="B113" s="2">
-        <v>372700</v>
+        <v>2100000</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>30</v>
@@ -7517,8 +7522,8 @@
       <c r="A114" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="B114" s="4">
-        <v>379420</v>
+      <c r="B114" s="2">
+        <v>2100000</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>30</v>
@@ -7553,7 +7558,7 @@
         <v>144</v>
       </c>
       <c r="B115" s="2">
-        <v>386200</v>
+        <v>2100000</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>30</v>
@@ -7587,8 +7592,8 @@
       <c r="A116" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B116" s="4">
-        <v>393040</v>
+      <c r="B116" s="2">
+        <v>2100000</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>30</v>
@@ -7623,7 +7628,7 @@
         <v>146</v>
       </c>
       <c r="B117" s="2">
-        <v>399940</v>
+        <v>2100000</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>30</v>
@@ -7657,8 +7662,8 @@
       <c r="A118" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B118" s="4">
-        <v>406900</v>
+      <c r="B118" s="2">
+        <v>2100000</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>30</v>
@@ -7693,7 +7698,7 @@
         <v>148</v>
       </c>
       <c r="B119" s="2">
-        <v>413920</v>
+        <v>2100000</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>30</v>
@@ -7727,8 +7732,8 @@
       <c r="A120" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B120" s="4">
-        <v>421000</v>
+      <c r="B120" s="2">
+        <v>2100000</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>30</v>
@@ -7763,7 +7768,7 @@
         <v>150</v>
       </c>
       <c r="B121" s="2">
-        <v>428140</v>
+        <v>2100000</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>30</v>
@@ -7797,8 +7802,8 @@
       <c r="A122" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B122" s="4">
-        <v>435340</v>
+      <c r="B122" s="2">
+        <v>2100000</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>30</v>
@@ -7833,7 +7838,7 @@
         <v>152</v>
       </c>
       <c r="B123" s="2">
-        <v>442600</v>
+        <v>2100000</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>30</v>
@@ -7867,8 +7872,8 @@
       <c r="A124" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B124" s="4">
-        <v>449920</v>
+      <c r="B124" s="2">
+        <v>2100000</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>30</v>
@@ -7903,7 +7908,7 @@
         <v>154</v>
       </c>
       <c r="B125" s="2">
-        <v>457300</v>
+        <v>2100000</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>30</v>
@@ -7937,8 +7942,8 @@
       <c r="A126" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B126" s="4">
-        <v>464740</v>
+      <c r="B126" s="2">
+        <v>2100000</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>30</v>
@@ -7973,7 +7978,7 @@
         <v>156</v>
       </c>
       <c r="B127" s="2">
-        <v>472240</v>
+        <v>2100000</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>30</v>
@@ -8007,8 +8012,8 @@
       <c r="A128" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B128" s="4">
-        <v>479800</v>
+      <c r="B128" s="2">
+        <v>2100000</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>30</v>
@@ -8043,7 +8048,7 @@
         <v>158</v>
       </c>
       <c r="B129" s="2">
-        <v>487420</v>
+        <v>2100000</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>30</v>
@@ -8077,8 +8082,8 @@
       <c r="A130" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="B130" s="4">
-        <v>495100</v>
+      <c r="B130" s="2">
+        <v>2100000</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>30</v>
@@ -8113,7 +8118,7 @@
         <v>160</v>
       </c>
       <c r="B131" s="2">
-        <v>502840</v>
+        <v>2100000</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>30</v>
@@ -8147,8 +8152,8 @@
       <c r="A132" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="B132" s="4">
-        <v>510640</v>
+      <c r="B132" s="2">
+        <v>2100000</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>30</v>
@@ -8183,7 +8188,7 @@
         <v>162</v>
       </c>
       <c r="B133" s="2">
-        <v>518500</v>
+        <v>2100000</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>30</v>
@@ -8217,8 +8222,8 @@
       <c r="A134" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B134" s="4">
-        <v>526420</v>
+      <c r="B134" s="2">
+        <v>2100000</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>30</v>
@@ -8253,7 +8258,7 @@
         <v>164</v>
       </c>
       <c r="B135" s="2">
-        <v>534400</v>
+        <v>2100000</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>30</v>
@@ -8287,8 +8292,8 @@
       <c r="A136" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B136" s="4">
-        <v>542440</v>
+      <c r="B136" s="2">
+        <v>2100000</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>30</v>
@@ -8323,7 +8328,7 @@
         <v>166</v>
       </c>
       <c r="B137" s="2">
-        <v>550540</v>
+        <v>2100000</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>30</v>
@@ -8357,8 +8362,8 @@
       <c r="A138" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B138" s="4">
-        <v>558700</v>
+      <c r="B138" s="2">
+        <v>2100000</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>30</v>
@@ -8393,7 +8398,7 @@
         <v>168</v>
       </c>
       <c r="B139" s="2">
-        <v>566920</v>
+        <v>2100000</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>30</v>
@@ -8427,8 +8432,8 @@
       <c r="A140" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B140" s="4">
-        <v>575200</v>
+      <c r="B140" s="2">
+        <v>2100000</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>30</v>
@@ -8463,7 +8468,7 @@
         <v>170</v>
       </c>
       <c r="B141" s="2">
-        <v>583540</v>
+        <v>2100000</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>30</v>
@@ -8497,8 +8502,8 @@
       <c r="A142" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B142" s="4">
-        <v>591940</v>
+      <c r="B142" s="2">
+        <v>2100000</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>30</v>
@@ -8533,7 +8538,7 @@
         <v>172</v>
       </c>
       <c r="B143" s="2">
-        <v>600400</v>
+        <v>2100000</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>30</v>
@@ -8567,8 +8572,8 @@
       <c r="A144" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B144" s="4">
-        <v>608920</v>
+      <c r="B144" s="2">
+        <v>2100000</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>30</v>
@@ -8603,7 +8608,7 @@
         <v>174</v>
       </c>
       <c r="B145" s="2">
-        <v>617500</v>
+        <v>2100000</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>30</v>
@@ -8637,8 +8642,8 @@
       <c r="A146" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B146" s="4">
-        <v>626140</v>
+      <c r="B146" s="2">
+        <v>2100000</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>30</v>
@@ -8673,7 +8678,7 @@
         <v>176</v>
       </c>
       <c r="B147" s="2">
-        <v>634840</v>
+        <v>2100000</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>30</v>
@@ -8707,8 +8712,8 @@
       <c r="A148" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B148" s="4">
-        <v>643600</v>
+      <c r="B148" s="2">
+        <v>2100000</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>30</v>
@@ -8743,7 +8748,7 @@
         <v>178</v>
       </c>
       <c r="B149" s="2">
-        <v>652420</v>
+        <v>2100000</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>30</v>
@@ -8777,8 +8782,8 @@
       <c r="A150" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B150" s="4">
-        <v>661300</v>
+      <c r="B150" s="2">
+        <v>2100000</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>30</v>
@@ -8813,7 +8818,7 @@
         <v>180</v>
       </c>
       <c r="B151" s="2">
-        <v>670240</v>
+        <v>2100000</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>30</v>
@@ -8847,8 +8852,8 @@
       <c r="A152" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B152" s="4">
-        <v>679240</v>
+      <c r="B152" s="2">
+        <v>2100000</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>30</v>
@@ -8883,7 +8888,7 @@
         <v>182</v>
       </c>
       <c r="B153" s="2">
-        <v>688300</v>
+        <v>2100000</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>30</v>
@@ -8917,8 +8922,8 @@
       <c r="A154" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="B154" s="4">
-        <v>697420</v>
+      <c r="B154" s="2">
+        <v>2100000</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>30</v>
